--- a/FCF_K13/V62_DIFFSET.xlsx
+++ b/FCF_K13/V62_DIFFSET.xlsx
@@ -34,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,9 +64,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4790,9 +4796,7 @@
       <c r="E2" t="n">
         <v>97.09999999999999</v>
       </c>
-      <c r="F2" t="n">
-        <v/>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -4848,9 +4852,7 @@
       <c r="E3" t="n">
         <v>113.1</v>
       </c>
-      <c r="F3" t="n">
-        <v/>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -4904,11 +4906,9 @@
         <v>-509.04</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F4" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -4962,11 +4962,9 @@
         <v>-453.598</v>
       </c>
       <c r="E5" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F5" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5020,11 +5018,9 @@
         <v>-406.026</v>
       </c>
       <c r="E6" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F6" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5061,58 +5057,60 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ALCAR</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>2025/03</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="2" t="n">
         <v>2259.664</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="2" t="n">
         <v>-381.301</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="2" t="n">
         <v>-116.9</v>
       </c>
-      <c r="F7" t="n">
-        <v/>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>KESİN</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>KESİN</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>EVET</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>BELGE</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="2" t="n">
         <v>-117.416</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="2" t="n">
         <v>183.997</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="2" t="n">
         <v>79.88800000000001</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Sistematik Evo hatası kontrolü (şirketin başka bir döneminde Evo belgeyle uyuşmadı) → Evo rakamı belgeyle uyuşmadı; belge rakamı (V7 2,259.7)</t>
         </is>
@@ -5138,9 +5136,7 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
-        <v/>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5196,9 +5192,7 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
-        <v/>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5254,9 +5248,7 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="n">
-        <v/>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -5312,9 +5304,7 @@
       <c r="E11" t="n">
         <v>14.9</v>
       </c>
-      <c r="F11" t="n">
-        <v/>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -5370,9 +5360,7 @@
       <c r="E12" t="n">
         <v>4</v>
       </c>
-      <c r="F12" t="n">
-        <v/>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -5428,9 +5416,7 @@
       <c r="E13" t="n">
         <v>-17.8</v>
       </c>
-      <c r="F13" t="n">
-        <v/>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -5486,9 +5472,7 @@
       <c r="E14" t="n">
         <v>5.9</v>
       </c>
-      <c r="F14" t="n">
-        <v/>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5544,9 +5528,7 @@
       <c r="E15" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F15" t="n">
-        <v/>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5602,9 +5584,7 @@
       <c r="E16" t="n">
         <v>23.3</v>
       </c>
-      <c r="F16" t="n">
-        <v/>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5660,9 +5640,7 @@
       <c r="E17" t="n">
         <v>0</v>
       </c>
-      <c r="F17" t="n">
-        <v/>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5716,11 +5694,9 @@
         <v>2138.938</v>
       </c>
       <c r="E18" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F18" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5776,9 +5752,7 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="F19" t="n">
-        <v/>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -5834,9 +5808,7 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="F20" t="n">
-        <v/>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5892,9 +5864,7 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
-      <c r="F21" t="n">
-        <v/>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5950,9 +5920,7 @@
       <c r="E22" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F22" t="n">
-        <v/>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6008,9 +5976,7 @@
       <c r="E23" t="n">
         <v>-3.6</v>
       </c>
-      <c r="F23" t="n">
-        <v/>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6066,9 +6032,7 @@
       <c r="E24" t="n">
         <v>-11.3</v>
       </c>
-      <c r="F24" t="n">
-        <v/>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6124,9 +6088,7 @@
       <c r="E25" t="n">
         <v>0</v>
       </c>
-      <c r="F25" t="n">
-        <v/>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6182,9 +6144,7 @@
       <c r="E26" t="n">
         <v>-31.2</v>
       </c>
-      <c r="F26" t="n">
-        <v/>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6240,9 +6200,7 @@
       <c r="E27" t="n">
         <v>0</v>
       </c>
-      <c r="F27" t="n">
-        <v/>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6296,11 +6254,9 @@
         <v>-351.894</v>
       </c>
       <c r="E28" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F28" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6356,9 +6312,7 @@
       <c r="E29" t="n">
         <v>0</v>
       </c>
-      <c r="F29" t="n">
-        <v/>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6414,9 +6368,7 @@
       <c r="E30" t="n">
         <v>0</v>
       </c>
-      <c r="F30" t="n">
-        <v/>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6472,9 +6424,7 @@
       <c r="E31" t="n">
         <v>0</v>
       </c>
-      <c r="F31" t="n">
-        <v/>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6528,11 +6478,9 @@
         <v>-770.915</v>
       </c>
       <c r="E32" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F32" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6588,9 +6536,7 @@
       <c r="E33" t="n">
         <v>-10.7</v>
       </c>
-      <c r="F33" t="n">
-        <v/>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6646,9 +6592,7 @@
       <c r="E34" t="n">
         <v>-15</v>
       </c>
-      <c r="F34" t="n">
-        <v/>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6704,9 +6648,7 @@
       <c r="E35" t="n">
         <v>-39.5</v>
       </c>
-      <c r="F35" t="n">
-        <v/>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6762,9 +6704,7 @@
       <c r="E36" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F36" t="n">
-        <v/>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6820,9 +6760,7 @@
       <c r="E37" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="F37" t="n">
-        <v/>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6878,9 +6816,7 @@
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="n">
-        <v/>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6934,11 +6870,9 @@
         <v>972.987</v>
       </c>
       <c r="E39" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F39" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6994,9 +6928,7 @@
       <c r="E40" t="n">
         <v>0</v>
       </c>
-      <c r="F40" t="n">
-        <v/>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -7050,11 +6982,9 @@
         <v>-132.54</v>
       </c>
       <c r="E41" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F41" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7110,9 +7040,7 @@
       <c r="E42" t="n">
         <v>0</v>
       </c>
-      <c r="F42" t="n">
-        <v/>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7166,11 +7094,9 @@
         <v>1847.836</v>
       </c>
       <c r="E43" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F43" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7226,9 +7152,7 @@
       <c r="E44" t="n">
         <v>0</v>
       </c>
-      <c r="F44" t="n">
-        <v/>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7284,9 +7208,7 @@
       <c r="E45" t="n">
         <v>-49.1</v>
       </c>
-      <c r="F45" t="n">
-        <v/>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -7342,9 +7264,7 @@
       <c r="E46" t="n">
         <v>-16.3</v>
       </c>
-      <c r="F46" t="n">
-        <v/>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -7398,11 +7318,9 @@
         <v>-784.277</v>
       </c>
       <c r="E47" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F47" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -7456,11 +7374,9 @@
         <v>-840.064</v>
       </c>
       <c r="E48" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F48" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -7516,9 +7432,7 @@
       <c r="E49" t="n">
         <v>-7.2</v>
       </c>
-      <c r="F49" t="n">
-        <v/>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7574,9 +7488,7 @@
       <c r="E50" t="n">
         <v>0</v>
       </c>
-      <c r="F50" t="n">
-        <v/>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7632,9 +7544,7 @@
       <c r="E51" t="n">
         <v>0</v>
       </c>
-      <c r="F51" t="n">
-        <v/>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7690,9 +7600,7 @@
       <c r="E52" t="n">
         <v>-72.40000000000001</v>
       </c>
-      <c r="F52" t="n">
-        <v/>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7748,9 +7656,7 @@
       <c r="E53" t="n">
         <v>0</v>
       </c>
-      <c r="F53" t="n">
-        <v/>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7806,9 +7712,7 @@
       <c r="E54" t="n">
         <v>0</v>
       </c>
-      <c r="F54" t="n">
-        <v/>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7864,9 +7768,7 @@
       <c r="E55" t="n">
         <v>-51.5</v>
       </c>
-      <c r="F55" t="n">
-        <v/>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7922,9 +7824,7 @@
       <c r="E56" t="n">
         <v>0</v>
       </c>
-      <c r="F56" t="n">
-        <v/>
-      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7980,9 +7880,7 @@
       <c r="E57" t="n">
         <v>0</v>
       </c>
-      <c r="F57" t="n">
-        <v/>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8038,9 +7936,7 @@
       <c r="E58" t="n">
         <v>0</v>
       </c>
-      <c r="F58" t="n">
-        <v/>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8096,9 +7992,7 @@
       <c r="E59" t="n">
         <v>0</v>
       </c>
-      <c r="F59" t="n">
-        <v/>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8154,9 +8048,7 @@
       <c r="E60" t="n">
         <v>0</v>
       </c>
-      <c r="F60" t="n">
-        <v/>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8210,11 +8102,9 @@
         <v>2038.437</v>
       </c>
       <c r="E61" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F61" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8251,116 +8141,120 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>GSDDE</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>2025/03</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="2" t="n">
         <v>-53.51800000000003</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="2" t="n">
         <v>2.213</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="2" t="n">
         <v>104.1</v>
       </c>
-      <c r="F62" t="n">
-        <v/>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>KESİN</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>KESİN</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>EVET</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>BELGE</t>
         </is>
       </c>
-      <c r="K62" t="n">
+      <c r="K62" s="2" t="n">
         <v>410.327</v>
       </c>
-      <c r="L62" t="n">
+      <c r="L62" s="2" t="n">
         <v>404.001</v>
       </c>
-      <c r="M62" t="n">
+      <c r="M62" s="2" t="n">
         <v>4.113</v>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>Sistematik Evo hatası kontrolü (şirketin başka bir döneminde Evo belgeyle uyuşmadı) → Evo rakamı belgeyle uyuşmadı; belge rakamı (V7 -53.5)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>GSDDE</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>2025/06</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="2" t="n">
         <v>-11.90399999999997</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="2" t="n">
         <v>43.828</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="2" t="n">
         <v>468.2</v>
       </c>
-      <c r="F63" t="n">
-        <v/>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>KESİN</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>KESİN</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>EVET</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>BELGE</t>
         </is>
       </c>
-      <c r="K63" t="n">
+      <c r="K63" s="2" t="n">
         <v>447.047</v>
       </c>
-      <c r="L63" t="n">
+      <c r="L63" s="2" t="n">
         <v>398.945</v>
       </c>
-      <c r="M63" t="n">
+      <c r="M63" s="2" t="n">
         <v>4.274</v>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>Sistematik Evo hatası kontrolü (şirketin başka bir döneminde Evo belgeyle uyuşmadı) → Evo rakamı belgeyle uyuşmadı; belge rakamı (V7 -11.9)</t>
         </is>
@@ -8384,11 +8278,9 @@
         <v>151.208</v>
       </c>
       <c r="E64" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F64" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8444,9 +8336,7 @@
       <c r="E65" t="n">
         <v>-40.3</v>
       </c>
-      <c r="F65" t="n">
-        <v/>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8502,9 +8392,7 @@
       <c r="E66" t="n">
         <v>-18.1</v>
       </c>
-      <c r="F66" t="n">
-        <v/>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8560,9 +8448,7 @@
       <c r="E67" t="n">
         <v>0</v>
       </c>
-      <c r="F67" t="n">
-        <v/>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8618,9 +8504,7 @@
       <c r="E68" t="n">
         <v>0</v>
       </c>
-      <c r="F68" t="n">
-        <v/>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8676,9 +8560,7 @@
       <c r="E69" t="n">
         <v>0</v>
       </c>
-      <c r="F69" t="n">
-        <v/>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -8734,9 +8616,7 @@
       <c r="E70" t="n">
         <v>36.7</v>
       </c>
-      <c r="F70" t="n">
-        <v/>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8792,9 +8672,7 @@
       <c r="E71" t="n">
         <v>33.3</v>
       </c>
-      <c r="F71" t="n">
-        <v/>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8848,11 +8726,9 @@
         <v>-858.465</v>
       </c>
       <c r="E72" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F72" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8906,11 +8782,9 @@
         <v>-438.889</v>
       </c>
       <c r="E73" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F73" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8966,9 +8840,7 @@
       <c r="E74" t="n">
         <v>0</v>
       </c>
-      <c r="F74" t="n">
-        <v/>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9024,9 +8896,7 @@
       <c r="E75" t="n">
         <v>-7335.3</v>
       </c>
-      <c r="F75" t="n">
-        <v/>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9080,11 +8950,9 @@
         <v>-652.2380000000001</v>
       </c>
       <c r="E76" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F76" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9138,11 +9006,9 @@
         <v>-657.917</v>
       </c>
       <c r="E77" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F77" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9196,11 +9062,9 @@
         <v>-771.954</v>
       </c>
       <c r="E78" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F78" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9256,9 +9120,7 @@
       <c r="E79" t="n">
         <v>76.2</v>
       </c>
-      <c r="F79" t="n">
-        <v/>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9314,9 +9176,7 @@
       <c r="E80" t="n">
         <v>6.7</v>
       </c>
-      <c r="F80" t="n">
-        <v/>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9372,9 +9232,7 @@
       <c r="E81" t="n">
         <v>-35.5</v>
       </c>
-      <c r="F81" t="n">
-        <v/>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9430,9 +9288,7 @@
       <c r="E82" t="n">
         <v>-62.6</v>
       </c>
-      <c r="F82" t="n">
-        <v/>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9488,9 +9344,7 @@
       <c r="E83" t="n">
         <v>0</v>
       </c>
-      <c r="F83" t="n">
-        <v/>
-      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9546,9 +9400,7 @@
       <c r="E84" t="n">
         <v>0</v>
       </c>
-      <c r="F84" t="n">
-        <v/>
-      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9604,9 +9456,7 @@
       <c r="E85" t="n">
         <v>0</v>
       </c>
-      <c r="F85" t="n">
-        <v/>
-      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9643,58 +9493,60 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>IZMDC</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>2025/06</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="C86" s="2" t="n">
         <v>121.025999999999</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="2" t="n">
         <v>-2021.3</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86" s="2" t="n">
         <v>-1770.1</v>
       </c>
-      <c r="F86" t="n">
-        <v/>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>KESİN</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>KESİN</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>EVET</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
         <is>
           <t>BELGE</t>
         </is>
       </c>
-      <c r="K86" t="n">
+      <c r="K86" s="2" t="n">
         <v>843.078</v>
       </c>
-      <c r="L86" t="n">
+      <c r="L86" s="2" t="n">
         <v>2782.783</v>
       </c>
-      <c r="M86" t="n">
+      <c r="M86" s="2" t="n">
         <v>81.595</v>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="N86" s="2" t="inlineStr">
         <is>
           <t>Sistematik Evo hatası kontrolü (şirketin başka bir döneminde Evo belgeyle uyuşmadı) → Evo rakamı belgeyle uyuşmadı; belge rakamı (V7 121.0)</t>
         </is>
@@ -9720,9 +9572,7 @@
       <c r="E87" t="n">
         <v>0</v>
       </c>
-      <c r="F87" t="n">
-        <v/>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9778,9 +9628,7 @@
       <c r="E88" t="n">
         <v>0</v>
       </c>
-      <c r="F88" t="n">
-        <v/>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9836,9 +9684,7 @@
       <c r="E89" t="n">
         <v>0</v>
       </c>
-      <c r="F89" t="n">
-        <v/>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9892,11 +9738,9 @@
         <v>-1648.407</v>
       </c>
       <c r="E90" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F90" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -9950,11 +9794,9 @@
         <v>-767.428</v>
       </c>
       <c r="E91" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F91" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -10008,11 +9850,9 @@
         <v>-1407.557</v>
       </c>
       <c r="E92" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F92" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10066,11 +9906,9 @@
         <v>934.352</v>
       </c>
       <c r="E93" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F93" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10126,9 +9964,7 @@
       <c r="E94" t="n">
         <v>0</v>
       </c>
-      <c r="F94" t="n">
-        <v/>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10182,11 +10018,9 @@
         <v>-2807.813</v>
       </c>
       <c r="E95" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F95" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -10240,11 +10074,9 @@
         <v>-2807.813</v>
       </c>
       <c r="E96" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F96" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -10298,11 +10130,9 @@
         <v>-2807.813</v>
       </c>
       <c r="E97" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F97" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -10358,9 +10188,7 @@
       <c r="E98" t="n">
         <v>0</v>
       </c>
-      <c r="F98" t="n">
-        <v/>
-      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10414,11 +10242,9 @@
         <v>246.838</v>
       </c>
       <c r="E99" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F99" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10472,11 +10298,9 @@
         <v>-609.551</v>
       </c>
       <c r="E100" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F100" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10513,58 +10337,60 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>KUVVA</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>2025/06</t>
         </is>
       </c>
-      <c r="C101" t="n">
+      <c r="C101" s="2" t="n">
         <v>-5.794999999999959</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="2" t="n">
         <v>1041.809</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101" s="2" t="n">
         <v>18077.7</v>
       </c>
-      <c r="F101" t="n">
-        <v/>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>KESİN</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>KESİN</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>EVET</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
         <is>
           <t>BELGE</t>
         </is>
       </c>
-      <c r="K101" t="n">
+      <c r="K101" s="2" t="n">
         <v>2376.27</v>
       </c>
-      <c r="L101" t="n">
+      <c r="L101" s="2" t="n">
         <v>1334.461</v>
       </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="inlineStr">
+      <c r="M101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
         <is>
           <t>Sistematik Evo hatası kontrolü (şirketin başka bir döneminde Evo belgeyle uyuşmadı) → Evo rakamı belgeyle uyuşmadı; belge rakamı (V7 -5.8)</t>
         </is>
@@ -10590,9 +10416,7 @@
       <c r="E102" t="n">
         <v>0</v>
       </c>
-      <c r="F102" t="n">
-        <v/>
-      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -10648,9 +10472,7 @@
       <c r="E103" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F103" t="n">
-        <v/>
-      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10706,9 +10528,7 @@
       <c r="E104" t="n">
         <v>0</v>
       </c>
-      <c r="F104" t="n">
-        <v/>
-      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10764,9 +10584,7 @@
       <c r="E105" t="n">
         <v>0</v>
       </c>
-      <c r="F105" t="n">
-        <v/>
-      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10822,9 +10640,7 @@
       <c r="E106" t="n">
         <v>0</v>
       </c>
-      <c r="F106" t="n">
-        <v/>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10880,9 +10696,7 @@
       <c r="E107" t="n">
         <v>6</v>
       </c>
-      <c r="F107" t="n">
-        <v/>
-      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10938,9 +10752,7 @@
       <c r="E108" t="n">
         <v>3.1</v>
       </c>
-      <c r="F108" t="n">
-        <v/>
-      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10994,11 +10806,9 @@
         <v>-615.0700000000001</v>
       </c>
       <c r="E109" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F109" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11054,9 +10864,7 @@
       <c r="E110" t="n">
         <v>0</v>
       </c>
-      <c r="F110" t="n">
-        <v/>
-      </c>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11110,11 +10918,9 @@
         <v>-2105.046</v>
       </c>
       <c r="E111" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F111" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11170,9 +10976,7 @@
       <c r="E112" t="n">
         <v>-32.3</v>
       </c>
-      <c r="F112" t="n">
-        <v/>
-      </c>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11228,9 +11032,7 @@
       <c r="E113" t="n">
         <v>-62.9</v>
       </c>
-      <c r="F113" t="n">
-        <v/>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11286,9 +11088,7 @@
       <c r="E114" t="n">
         <v>-52.3</v>
       </c>
-      <c r="F114" t="n">
-        <v/>
-      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11344,9 +11144,7 @@
       <c r="E115" t="n">
         <v>-64.7</v>
       </c>
-      <c r="F115" t="n">
-        <v/>
-      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11402,9 +11200,7 @@
       <c r="E116" t="n">
         <v>-17.8</v>
       </c>
-      <c r="F116" t="n">
-        <v/>
-      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11460,9 +11256,7 @@
       <c r="E117" t="n">
         <v>0</v>
       </c>
-      <c r="F117" t="n">
-        <v/>
-      </c>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -11518,9 +11312,7 @@
       <c r="E118" t="n">
         <v>0</v>
       </c>
-      <c r="F118" t="n">
-        <v/>
-      </c>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -11574,11 +11366,9 @@
         <v>244.415</v>
       </c>
       <c r="E119" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F119" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11634,9 +11424,7 @@
       <c r="E120" t="n">
         <v>0</v>
       </c>
-      <c r="F120" t="n">
-        <v/>
-      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11690,11 +11478,9 @@
         <v>-1015.452</v>
       </c>
       <c r="E121" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F121" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11750,9 +11536,7 @@
       <c r="E122" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F122" t="n">
-        <v/>
-      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11808,9 +11592,7 @@
       <c r="E123" t="n">
         <v>-8</v>
       </c>
-      <c r="F123" t="n">
-        <v/>
-      </c>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11866,9 +11648,7 @@
       <c r="E124" t="n">
         <v>24.6</v>
       </c>
-      <c r="F124" t="n">
-        <v/>
-      </c>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11924,9 +11704,7 @@
       <c r="E125" t="n">
         <v>12.8</v>
       </c>
-      <c r="F125" t="n">
-        <v/>
-      </c>
+      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11982,9 +11760,7 @@
       <c r="E126" t="n">
         <v>0</v>
       </c>
-      <c r="F126" t="n">
-        <v/>
-      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12040,9 +11816,7 @@
       <c r="E127" t="n">
         <v>0</v>
       </c>
-      <c r="F127" t="n">
-        <v/>
-      </c>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12098,9 +11872,7 @@
       <c r="E128" t="n">
         <v>-64.7</v>
       </c>
-      <c r="F128" t="n">
-        <v/>
-      </c>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12156,9 +11928,7 @@
       <c r="E129" t="n">
         <v>-36.7</v>
       </c>
-      <c r="F129" t="n">
-        <v/>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12214,9 +11984,7 @@
       <c r="E130" t="n">
         <v>0</v>
       </c>
-      <c r="F130" t="n">
-        <v/>
-      </c>
+      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12270,11 +12038,9 @@
         <v>225.589</v>
       </c>
       <c r="E131" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F131" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12328,11 +12094,9 @@
         <v>200.311</v>
       </c>
       <c r="E132" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F132" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12388,9 +12152,7 @@
       <c r="E133" t="n">
         <v>0</v>
       </c>
-      <c r="F133" t="n">
-        <v/>
-      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12446,9 +12208,7 @@
       <c r="E134" t="n">
         <v>0</v>
       </c>
-      <c r="F134" t="n">
-        <v/>
-      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12504,9 +12264,7 @@
       <c r="E135" t="n">
         <v>0</v>
       </c>
-      <c r="F135" t="n">
-        <v/>
-      </c>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12562,9 +12320,7 @@
       <c r="E136" t="n">
         <v>0</v>
       </c>
-      <c r="F136" t="n">
-        <v/>
-      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12620,9 +12376,7 @@
       <c r="E137" t="n">
         <v>0</v>
       </c>
-      <c r="F137" t="n">
-        <v/>
-      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12676,11 +12430,9 @@
         <v>188.421</v>
       </c>
       <c r="E138" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F138" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12734,11 +12486,9 @@
         <v>9.602</v>
       </c>
       <c r="E139" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F139" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12794,9 +12544,7 @@
       <c r="E140" t="n">
         <v>14.6</v>
       </c>
-      <c r="F140" t="n">
-        <v/>
-      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12852,9 +12600,7 @@
       <c r="E141" t="n">
         <v>52.3</v>
       </c>
-      <c r="F141" t="n">
-        <v/>
-      </c>
+      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12908,11 +12654,9 @@
         <v>-649.955</v>
       </c>
       <c r="E142" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F142" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12966,11 +12710,9 @@
         <v>156.391</v>
       </c>
       <c r="E143" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F143" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13024,11 +12766,9 @@
         <v>169.908</v>
       </c>
       <c r="E144" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F144" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13084,9 +12824,7 @@
       <c r="E145" t="n">
         <v>-8.4</v>
       </c>
-      <c r="F145" t="n">
-        <v/>
-      </c>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13142,9 +12880,7 @@
       <c r="E146" t="n">
         <v>-9.4</v>
       </c>
-      <c r="F146" t="n">
-        <v/>
-      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13200,9 +12936,7 @@
       <c r="E147" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F147" t="n">
-        <v/>
-      </c>
+      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13258,9 +12992,7 @@
       <c r="E148" t="n">
         <v>-1</v>
       </c>
-      <c r="F148" t="n">
-        <v/>
-      </c>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13316,9 +13048,7 @@
       <c r="E149" t="n">
         <v>17.1</v>
       </c>
-      <c r="F149" t="n">
-        <v/>
-      </c>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13374,9 +13104,7 @@
       <c r="E150" t="n">
         <v>367.7</v>
       </c>
-      <c r="F150" t="n">
-        <v/>
-      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -13432,9 +13160,7 @@
       <c r="E151" t="n">
         <v>0</v>
       </c>
-      <c r="F151" t="n">
-        <v/>
-      </c>
+      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13490,9 +13216,7 @@
       <c r="E152" t="n">
         <v>0</v>
       </c>
-      <c r="F152" t="n">
-        <v/>
-      </c>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13548,9 +13272,7 @@
       <c r="E153" t="n">
         <v>0</v>
       </c>
-      <c r="F153" t="n">
-        <v/>
-      </c>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13587,116 +13309,120 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>SMART</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>2025/03</t>
         </is>
       </c>
-      <c r="C154" t="n">
+      <c r="C154" s="2" t="n">
         <v>9.475000000000012</v>
       </c>
-      <c r="D154" t="n">
+      <c r="D154" s="2" t="n">
         <v>-47.207</v>
       </c>
-      <c r="E154" t="n">
+      <c r="E154" s="2" t="n">
         <v>-598.2</v>
       </c>
-      <c r="F154" t="n">
-        <v/>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>KESİN</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>KESİN</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>EVET</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
         <is>
           <t>BELGE</t>
         </is>
       </c>
-      <c r="K154" t="n">
+      <c r="K154" s="2" t="n">
         <v>168.467</v>
       </c>
-      <c r="L154" t="n">
+      <c r="L154" s="2" t="n">
         <v>214.154</v>
       </c>
-      <c r="M154" t="n">
+      <c r="M154" s="2" t="n">
         <v>1.52</v>
       </c>
-      <c r="N154" t="inlineStr">
+      <c r="N154" s="2" t="inlineStr">
         <is>
           <t>Sistematik Evo hatası kontrolü (şirketin başka bir döneminde Evo belgeyle uyuşmadı) → Evo rakamı belgeyle uyuşmadı; belge rakamı (V7 9.5)</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>SMART</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>2025/06</t>
         </is>
       </c>
-      <c r="C155" t="n">
+      <c r="C155" s="2" t="n">
         <v>7.325000000000009</v>
       </c>
-      <c r="D155" t="n">
+      <c r="D155" s="2" t="n">
         <v>-49.358</v>
       </c>
-      <c r="E155" t="n">
+      <c r="E155" s="2" t="n">
         <v>-773.8</v>
       </c>
-      <c r="F155" t="n">
-        <v/>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>KESİN</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>KESİN</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>EVET</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
         <is>
           <t>BELGE</t>
         </is>
       </c>
-      <c r="K155" t="n">
+      <c r="K155" s="2" t="n">
         <v>151.335</v>
       </c>
-      <c r="L155" t="n">
+      <c r="L155" s="2" t="n">
         <v>199</v>
       </c>
-      <c r="M155" t="n">
+      <c r="M155" s="2" t="n">
         <v>1.693</v>
       </c>
-      <c r="N155" t="inlineStr">
+      <c r="N155" s="2" t="inlineStr">
         <is>
           <t>Sistematik Evo hatası kontrolü (şirketin başka bir döneminde Evo belgeyle uyuşmadı) → Evo rakamı belgeyle uyuşmadı; belge rakamı (V7 7.3)</t>
         </is>
@@ -13722,9 +13448,7 @@
       <c r="E156" t="n">
         <v>0</v>
       </c>
-      <c r="F156" t="n">
-        <v/>
-      </c>
+      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13780,9 +13504,7 @@
       <c r="E157" t="n">
         <v>0.1</v>
       </c>
-      <c r="F157" t="n">
-        <v/>
-      </c>
+      <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13838,9 +13560,7 @@
       <c r="E158" t="n">
         <v>0.1</v>
       </c>
-      <c r="F158" t="n">
-        <v/>
-      </c>
+      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13896,9 +13616,7 @@
       <c r="E159" t="n">
         <v>-27.9</v>
       </c>
-      <c r="F159" t="n">
-        <v/>
-      </c>
+      <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13954,9 +13672,7 @@
       <c r="E160" t="n">
         <v>-49.6</v>
       </c>
-      <c r="F160" t="n">
-        <v/>
-      </c>
+      <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14012,9 +13728,7 @@
       <c r="E161" t="n">
         <v>-6.6</v>
       </c>
-      <c r="F161" t="n">
-        <v/>
-      </c>
+      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14070,9 +13784,7 @@
       <c r="E162" t="n">
         <v>-7.5</v>
       </c>
-      <c r="F162" t="n">
-        <v/>
-      </c>
+      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14128,9 +13840,7 @@
       <c r="E163" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F163" t="n">
-        <v/>
-      </c>
+      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14184,11 +13894,9 @@
         <v>275.087</v>
       </c>
       <c r="E164" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F164" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14242,11 +13950,9 @@
         <v>554.2569999999999</v>
       </c>
       <c r="E165" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F165" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14302,9 +14008,7 @@
       <c r="E166" t="n">
         <v>-65</v>
       </c>
-      <c r="F166" t="n">
-        <v/>
-      </c>
+      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14360,9 +14064,7 @@
       <c r="E167" t="n">
         <v>0</v>
       </c>
-      <c r="F167" t="n">
-        <v/>
-      </c>
+      <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14418,9 +14120,7 @@
       <c r="E168" t="n">
         <v>0</v>
       </c>
-      <c r="F168" t="n">
-        <v/>
-      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14476,9 +14176,7 @@
       <c r="E169" t="n">
         <v>0</v>
       </c>
-      <c r="F169" t="n">
-        <v/>
-      </c>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14534,9 +14232,7 @@
       <c r="E170" t="n">
         <v>0</v>
       </c>
-      <c r="F170" t="n">
-        <v/>
-      </c>
+      <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14592,9 +14288,7 @@
       <c r="E171" t="n">
         <v>4</v>
       </c>
-      <c r="F171" t="n">
-        <v/>
-      </c>
+      <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -14650,9 +14344,7 @@
       <c r="E172" t="n">
         <v>-54.6</v>
       </c>
-      <c r="F172" t="n">
-        <v/>
-      </c>
+      <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -14708,9 +14400,7 @@
       <c r="E173" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F173" t="n">
-        <v/>
-      </c>
+      <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14766,9 +14456,7 @@
       <c r="E174" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F174" t="n">
-        <v/>
-      </c>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -14824,9 +14512,7 @@
       <c r="E175" t="n">
         <v>0</v>
       </c>
-      <c r="F175" t="n">
-        <v/>
-      </c>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14880,11 +14566,9 @@
         <v>5914.446</v>
       </c>
       <c r="E176" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F176" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14940,9 +14624,7 @@
       <c r="E177" t="n">
         <v>0</v>
       </c>
-      <c r="F177" t="n">
-        <v/>
-      </c>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14998,9 +14680,7 @@
       <c r="E178" t="n">
         <v>22.1</v>
       </c>
-      <c r="F178" t="n">
-        <v/>
-      </c>
+      <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15056,9 +14736,7 @@
       <c r="E179" t="n">
         <v>0</v>
       </c>
-      <c r="F179" t="n">
-        <v/>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15112,11 +14790,9 @@
         <v>3682.719</v>
       </c>
       <c r="E180" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F180" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15172,9 +14848,7 @@
       <c r="E181" t="n">
         <v>0</v>
       </c>
-      <c r="F181" t="n">
-        <v/>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15230,9 +14904,7 @@
       <c r="E182" t="n">
         <v>-10</v>
       </c>
-      <c r="F182" t="n">
-        <v/>
-      </c>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -15288,9 +14960,7 @@
       <c r="E183" t="n">
         <v>22.2</v>
       </c>
-      <c r="F183" t="n">
-        <v/>
-      </c>
+      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15344,11 +15014,9 @@
         <v>-1157.812</v>
       </c>
       <c r="E184" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F184" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15404,9 +15072,7 @@
       <c r="E185" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F185" t="n">
-        <v/>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15460,11 +15126,9 @@
         <v>-2456.823</v>
       </c>
       <c r="E186" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F186" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15520,9 +15184,7 @@
       <c r="E187" t="n">
         <v>0</v>
       </c>
-      <c r="F187" t="n">
-        <v/>
-      </c>
+      <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15578,9 +15240,7 @@
       <c r="E188" t="n">
         <v>0</v>
       </c>
-      <c r="F188" t="n">
-        <v/>
-      </c>
+      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15627,14 +15287,10 @@
           <t>2025/06</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
       <c r="D189" t="n">
         <v>-0.887</v>
       </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="n">
-        <v/>
-      </c>
+      <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
           <t>NULL</t>
@@ -15690,9 +15346,7 @@
       <c r="E190" t="n">
         <v>-22.6</v>
       </c>
-      <c r="F190" t="n">
-        <v/>
-      </c>
+      <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15748,9 +15402,7 @@
       <c r="E191" t="n">
         <v>7</v>
       </c>
-      <c r="F191" t="n">
-        <v/>
-      </c>
+      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15804,11 +15456,9 @@
         <v>-435.993</v>
       </c>
       <c r="E192" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F192" t="n">
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15864,9 +15514,7 @@
       <c r="E193" t="n">
         <v>0</v>
       </c>
-      <c r="F193" t="n">
-        <v/>
-      </c>
+      <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15922,9 +15570,7 @@
       <c r="E194" t="n">
         <v>0</v>
       </c>
-      <c r="F194" t="n">
-        <v/>
-      </c>
+      <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
           <t>KESİN</t>

--- a/FCF_K13/V62_DIFFSET.xlsx
+++ b/FCF_K13/V62_DIFFSET.xlsx
@@ -12,6 +12,9 @@
     <sheet name="FUNNEL_DEGISEN" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="FCF_SISTEM" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="FUNNEL_SISTEM" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="K9_DEGISEN" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="K9_KOSULLU_KALAN" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="K9_FUNNEL" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,6 +508,42 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>Bu düzeltmeler sonucunda Funnel puanı/kategorisi değişen satırlar (4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>K9_DEGISEN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kontrol 9 (yatırım bölümü "Diğer" artığı) belgeden sınıflandı: 140 satır KOŞULLU→KESİN; ARASE (6 dönem) ve UNLU (3 dönem) "Diğer" içindeki yatırım harcaması CAPEX'e eklendi, FCF düştü.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>K9_KOSULLU_KALAN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kontrol 9 sonrası KOŞULLU kalanlar: "Diğer" içeriği dipnotta açıklanmıyor (12) ve ATATP Kontrol 11 sunum değişikliği (2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>K9_FUNNEL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bu değişikliğin Funnel etkisi.</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4835,6 @@
       <c r="E2" t="n">
         <v>97.09999999999999</v>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -4852,7 +4890,6 @@
       <c r="E3" t="n">
         <v>113.1</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -4908,7 +4945,6 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -4964,7 +5000,6 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5020,7 +5055,6 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5136,7 +5170,6 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5192,7 +5225,6 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5248,7 +5280,6 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -5304,7 +5335,6 @@
       <c r="E11" t="n">
         <v>14.9</v>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -5360,7 +5390,6 @@
       <c r="E12" t="n">
         <v>4</v>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -5416,7 +5445,6 @@
       <c r="E13" t="n">
         <v>-17.8</v>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -5472,7 +5500,6 @@
       <c r="E14" t="n">
         <v>5.9</v>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5528,7 +5555,6 @@
       <c r="E15" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5584,7 +5610,6 @@
       <c r="E16" t="n">
         <v>23.3</v>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5640,7 +5665,6 @@
       <c r="E17" t="n">
         <v>0</v>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5696,7 +5720,6 @@
       <c r="E18" t="n">
         <v>0</v>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5752,7 +5775,6 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -5808,7 +5830,6 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5864,7 +5885,6 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -5920,7 +5940,6 @@
       <c r="E22" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -5976,7 +5995,6 @@
       <c r="E23" t="n">
         <v>-3.6</v>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6032,7 +6050,6 @@
       <c r="E24" t="n">
         <v>-11.3</v>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6088,7 +6105,6 @@
       <c r="E25" t="n">
         <v>0</v>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6144,7 +6160,6 @@
       <c r="E26" t="n">
         <v>-31.2</v>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6200,7 +6215,6 @@
       <c r="E27" t="n">
         <v>0</v>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6256,7 +6270,6 @@
       <c r="E28" t="n">
         <v>0</v>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6312,7 +6325,6 @@
       <c r="E29" t="n">
         <v>0</v>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6368,7 +6380,6 @@
       <c r="E30" t="n">
         <v>0</v>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6424,7 +6435,6 @@
       <c r="E31" t="n">
         <v>0</v>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6480,7 +6490,6 @@
       <c r="E32" t="n">
         <v>0</v>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6536,7 +6545,6 @@
       <c r="E33" t="n">
         <v>-10.7</v>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6592,7 +6600,6 @@
       <c r="E34" t="n">
         <v>-15</v>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6648,7 +6655,6 @@
       <c r="E35" t="n">
         <v>-39.5</v>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6704,7 +6710,6 @@
       <c r="E36" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6760,7 +6765,6 @@
       <c r="E37" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -6816,7 +6820,6 @@
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6872,7 +6875,6 @@
       <c r="E39" t="n">
         <v>0</v>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6928,7 +6930,6 @@
       <c r="E40" t="n">
         <v>0</v>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -6984,7 +6985,6 @@
       <c r="E41" t="n">
         <v>0</v>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7040,7 +7040,6 @@
       <c r="E42" t="n">
         <v>0</v>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7096,7 +7095,6 @@
       <c r="E43" t="n">
         <v>0</v>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7152,7 +7150,6 @@
       <c r="E44" t="n">
         <v>0</v>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7208,7 +7205,6 @@
       <c r="E45" t="n">
         <v>-49.1</v>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -7264,7 +7260,6 @@
       <c r="E46" t="n">
         <v>-16.3</v>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -7320,7 +7315,6 @@
       <c r="E47" t="n">
         <v>0</v>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -7376,7 +7370,6 @@
       <c r="E48" t="n">
         <v>0</v>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -7432,7 +7425,6 @@
       <c r="E49" t="n">
         <v>-7.2</v>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7488,7 +7480,6 @@
       <c r="E50" t="n">
         <v>0</v>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7544,7 +7535,6 @@
       <c r="E51" t="n">
         <v>0</v>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7600,7 +7590,6 @@
       <c r="E52" t="n">
         <v>-72.40000000000001</v>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7656,7 +7645,6 @@
       <c r="E53" t="n">
         <v>0</v>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7712,7 +7700,6 @@
       <c r="E54" t="n">
         <v>0</v>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7768,7 +7755,6 @@
       <c r="E55" t="n">
         <v>-51.5</v>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7824,7 +7810,6 @@
       <c r="E56" t="n">
         <v>0</v>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7880,7 +7865,6 @@
       <c r="E57" t="n">
         <v>0</v>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7936,7 +7920,6 @@
       <c r="E58" t="n">
         <v>0</v>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -7992,7 +7975,6 @@
       <c r="E59" t="n">
         <v>0</v>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8048,7 +8030,6 @@
       <c r="E60" t="n">
         <v>0</v>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8104,7 +8085,6 @@
       <c r="E61" t="n">
         <v>0</v>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8280,7 +8260,6 @@
       <c r="E64" t="n">
         <v>0</v>
       </c>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8336,7 +8315,6 @@
       <c r="E65" t="n">
         <v>-40.3</v>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8392,7 +8370,6 @@
       <c r="E66" t="n">
         <v>-18.1</v>
       </c>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8448,7 +8425,6 @@
       <c r="E67" t="n">
         <v>0</v>
       </c>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8504,7 +8480,6 @@
       <c r="E68" t="n">
         <v>0</v>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8560,7 +8535,6 @@
       <c r="E69" t="n">
         <v>0</v>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -8616,7 +8590,6 @@
       <c r="E70" t="n">
         <v>36.7</v>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8672,7 +8645,6 @@
       <c r="E71" t="n">
         <v>33.3</v>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8728,7 +8700,6 @@
       <c r="E72" t="n">
         <v>0</v>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8784,7 +8755,6 @@
       <c r="E73" t="n">
         <v>0</v>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8840,7 +8810,6 @@
       <c r="E74" t="n">
         <v>0</v>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8896,7 +8865,6 @@
       <c r="E75" t="n">
         <v>-7335.3</v>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -8952,7 +8920,6 @@
       <c r="E76" t="n">
         <v>0</v>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9008,7 +8975,6 @@
       <c r="E77" t="n">
         <v>0</v>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9064,7 +9030,6 @@
       <c r="E78" t="n">
         <v>0</v>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9120,7 +9085,6 @@
       <c r="E79" t="n">
         <v>76.2</v>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9176,7 +9140,6 @@
       <c r="E80" t="n">
         <v>6.7</v>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9232,7 +9195,6 @@
       <c r="E81" t="n">
         <v>-35.5</v>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9288,7 +9250,6 @@
       <c r="E82" t="n">
         <v>-62.6</v>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9344,7 +9305,6 @@
       <c r="E83" t="n">
         <v>0</v>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9400,7 +9360,6 @@
       <c r="E84" t="n">
         <v>0</v>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9456,7 +9415,6 @@
       <c r="E85" t="n">
         <v>0</v>
       </c>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9572,7 +9530,6 @@
       <c r="E87" t="n">
         <v>0</v>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9628,7 +9585,6 @@
       <c r="E88" t="n">
         <v>0</v>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9684,7 +9640,6 @@
       <c r="E89" t="n">
         <v>0</v>
       </c>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9740,7 +9695,6 @@
       <c r="E90" t="n">
         <v>0</v>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -9796,7 +9750,6 @@
       <c r="E91" t="n">
         <v>0</v>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -9852,7 +9805,6 @@
       <c r="E92" t="n">
         <v>0</v>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9908,7 +9860,6 @@
       <c r="E93" t="n">
         <v>0</v>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -9964,7 +9915,6 @@
       <c r="E94" t="n">
         <v>0</v>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10020,7 +9970,6 @@
       <c r="E95" t="n">
         <v>0</v>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -10076,7 +10025,6 @@
       <c r="E96" t="n">
         <v>0</v>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -10132,7 +10080,6 @@
       <c r="E97" t="n">
         <v>0</v>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -10188,7 +10135,6 @@
       <c r="E98" t="n">
         <v>0</v>
       </c>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10244,7 +10190,6 @@
       <c r="E99" t="n">
         <v>0</v>
       </c>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10300,7 +10245,6 @@
       <c r="E100" t="n">
         <v>0</v>
       </c>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10416,7 +10360,6 @@
       <c r="E102" t="n">
         <v>0</v>
       </c>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -10472,7 +10415,6 @@
       <c r="E103" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10528,7 +10470,6 @@
       <c r="E104" t="n">
         <v>0</v>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10584,7 +10525,6 @@
       <c r="E105" t="n">
         <v>0</v>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10640,7 +10580,6 @@
       <c r="E106" t="n">
         <v>0</v>
       </c>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10696,7 +10635,6 @@
       <c r="E107" t="n">
         <v>6</v>
       </c>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10752,7 +10690,6 @@
       <c r="E108" t="n">
         <v>3.1</v>
       </c>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10808,7 +10745,6 @@
       <c r="E109" t="n">
         <v>0</v>
       </c>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10864,7 +10800,6 @@
       <c r="E110" t="n">
         <v>0</v>
       </c>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10920,7 +10855,6 @@
       <c r="E111" t="n">
         <v>0</v>
       </c>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -10976,7 +10910,6 @@
       <c r="E112" t="n">
         <v>-32.3</v>
       </c>
-      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11032,7 +10965,6 @@
       <c r="E113" t="n">
         <v>-62.9</v>
       </c>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11088,7 +11020,6 @@
       <c r="E114" t="n">
         <v>-52.3</v>
       </c>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11144,7 +11075,6 @@
       <c r="E115" t="n">
         <v>-64.7</v>
       </c>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11200,7 +11130,6 @@
       <c r="E116" t="n">
         <v>-17.8</v>
       </c>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11256,7 +11185,6 @@
       <c r="E117" t="n">
         <v>0</v>
       </c>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -11312,7 +11240,6 @@
       <c r="E118" t="n">
         <v>0</v>
       </c>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -11368,7 +11295,6 @@
       <c r="E119" t="n">
         <v>0</v>
       </c>
-      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11424,7 +11350,6 @@
       <c r="E120" t="n">
         <v>0</v>
       </c>
-      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11480,7 +11405,6 @@
       <c r="E121" t="n">
         <v>0</v>
       </c>
-      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11536,7 +11460,6 @@
       <c r="E122" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11592,7 +11515,6 @@
       <c r="E123" t="n">
         <v>-8</v>
       </c>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11648,7 +11570,6 @@
       <c r="E124" t="n">
         <v>24.6</v>
       </c>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11704,7 +11625,6 @@
       <c r="E125" t="n">
         <v>12.8</v>
       </c>
-      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11760,7 +11680,6 @@
       <c r="E126" t="n">
         <v>0</v>
       </c>
-      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11816,7 +11735,6 @@
       <c r="E127" t="n">
         <v>0</v>
       </c>
-      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11872,7 +11790,6 @@
       <c r="E128" t="n">
         <v>-64.7</v>
       </c>
-      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11928,7 +11845,6 @@
       <c r="E129" t="n">
         <v>-36.7</v>
       </c>
-      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -11984,7 +11900,6 @@
       <c r="E130" t="n">
         <v>0</v>
       </c>
-      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12040,7 +11955,6 @@
       <c r="E131" t="n">
         <v>0</v>
       </c>
-      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12096,7 +12010,6 @@
       <c r="E132" t="n">
         <v>0</v>
       </c>
-      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12152,7 +12065,6 @@
       <c r="E133" t="n">
         <v>0</v>
       </c>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12208,7 +12120,6 @@
       <c r="E134" t="n">
         <v>0</v>
       </c>
-      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12264,7 +12175,6 @@
       <c r="E135" t="n">
         <v>0</v>
       </c>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12320,7 +12230,6 @@
       <c r="E136" t="n">
         <v>0</v>
       </c>
-      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12376,7 +12285,6 @@
       <c r="E137" t="n">
         <v>0</v>
       </c>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12432,7 +12340,6 @@
       <c r="E138" t="n">
         <v>0</v>
       </c>
-      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12488,7 +12395,6 @@
       <c r="E139" t="n">
         <v>0</v>
       </c>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12544,7 +12450,6 @@
       <c r="E140" t="n">
         <v>14.6</v>
       </c>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12600,7 +12505,6 @@
       <c r="E141" t="n">
         <v>52.3</v>
       </c>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12656,7 +12560,6 @@
       <c r="E142" t="n">
         <v>0</v>
       </c>
-      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12712,7 +12615,6 @@
       <c r="E143" t="n">
         <v>0</v>
       </c>
-      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12768,7 +12670,6 @@
       <c r="E144" t="n">
         <v>0</v>
       </c>
-      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12824,7 +12725,6 @@
       <c r="E145" t="n">
         <v>-8.4</v>
       </c>
-      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12880,7 +12780,6 @@
       <c r="E146" t="n">
         <v>-9.4</v>
       </c>
-      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12936,7 +12835,6 @@
       <c r="E147" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -12992,7 +12890,6 @@
       <c r="E148" t="n">
         <v>-1</v>
       </c>
-      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13048,7 +12945,6 @@
       <c r="E149" t="n">
         <v>17.1</v>
       </c>
-      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13104,7 +13000,6 @@
       <c r="E150" t="n">
         <v>367.7</v>
       </c>
-      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -13160,7 +13055,6 @@
       <c r="E151" t="n">
         <v>0</v>
       </c>
-      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13216,7 +13110,6 @@
       <c r="E152" t="n">
         <v>0</v>
       </c>
-      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13272,7 +13165,6 @@
       <c r="E153" t="n">
         <v>0</v>
       </c>
-      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13448,7 +13340,6 @@
       <c r="E156" t="n">
         <v>0</v>
       </c>
-      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13504,7 +13395,6 @@
       <c r="E157" t="n">
         <v>0.1</v>
       </c>
-      <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13560,7 +13450,6 @@
       <c r="E158" t="n">
         <v>0.1</v>
       </c>
-      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13616,7 +13505,6 @@
       <c r="E159" t="n">
         <v>-27.9</v>
       </c>
-      <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13672,7 +13560,6 @@
       <c r="E160" t="n">
         <v>-49.6</v>
       </c>
-      <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13728,7 +13615,6 @@
       <c r="E161" t="n">
         <v>-6.6</v>
       </c>
-      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13784,7 +13670,6 @@
       <c r="E162" t="n">
         <v>-7.5</v>
       </c>
-      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13840,7 +13725,6 @@
       <c r="E163" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13896,7 +13780,6 @@
       <c r="E164" t="n">
         <v>0</v>
       </c>
-      <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -13952,7 +13835,6 @@
       <c r="E165" t="n">
         <v>0</v>
       </c>
-      <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14008,7 +13890,6 @@
       <c r="E166" t="n">
         <v>-65</v>
       </c>
-      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14064,7 +13945,6 @@
       <c r="E167" t="n">
         <v>0</v>
       </c>
-      <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14120,7 +14000,6 @@
       <c r="E168" t="n">
         <v>0</v>
       </c>
-      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14176,7 +14055,6 @@
       <c r="E169" t="n">
         <v>0</v>
       </c>
-      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14232,7 +14110,6 @@
       <c r="E170" t="n">
         <v>0</v>
       </c>
-      <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14288,7 +14165,6 @@
       <c r="E171" t="n">
         <v>4</v>
       </c>
-      <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -14344,7 +14220,6 @@
       <c r="E172" t="n">
         <v>-54.6</v>
       </c>
-      <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -14400,7 +14275,6 @@
       <c r="E173" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14456,7 +14330,6 @@
       <c r="E174" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -14512,7 +14385,6 @@
       <c r="E175" t="n">
         <v>0</v>
       </c>
-      <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14568,7 +14440,6 @@
       <c r="E176" t="n">
         <v>0</v>
       </c>
-      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14624,7 +14495,6 @@
       <c r="E177" t="n">
         <v>0</v>
       </c>
-      <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14680,7 +14550,6 @@
       <c r="E178" t="n">
         <v>22.1</v>
       </c>
-      <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14736,7 +14605,6 @@
       <c r="E179" t="n">
         <v>0</v>
       </c>
-      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14792,7 +14660,6 @@
       <c r="E180" t="n">
         <v>0</v>
       </c>
-      <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14848,7 +14715,6 @@
       <c r="E181" t="n">
         <v>0</v>
       </c>
-      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -14904,7 +14770,6 @@
       <c r="E182" t="n">
         <v>-10</v>
       </c>
-      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
           <t>TÜRETİLMİŞ</t>
@@ -14960,7 +14825,6 @@
       <c r="E183" t="n">
         <v>22.2</v>
       </c>
-      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15016,7 +14880,6 @@
       <c r="E184" t="n">
         <v>0</v>
       </c>
-      <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15072,7 +14935,6 @@
       <c r="E185" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15128,7 +14990,6 @@
       <c r="E186" t="n">
         <v>0</v>
       </c>
-      <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15184,7 +15045,6 @@
       <c r="E187" t="n">
         <v>0</v>
       </c>
-      <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15240,7 +15100,6 @@
       <c r="E188" t="n">
         <v>0</v>
       </c>
-      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15290,7 +15149,6 @@
       <c r="D189" t="n">
         <v>-0.887</v>
       </c>
-      <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
           <t>NULL</t>
@@ -15346,7 +15204,6 @@
       <c r="E190" t="n">
         <v>-22.6</v>
       </c>
-      <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15402,7 +15259,6 @@
       <c r="E191" t="n">
         <v>7</v>
       </c>
-      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15458,7 +15314,6 @@
       <c r="E192" t="n">
         <v>0</v>
       </c>
-      <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15514,7 +15369,6 @@
       <c r="E193" t="n">
         <v>0</v>
       </c>
-      <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15570,7 +15424,6 @@
       <c r="E194" t="n">
         <v>0</v>
       </c>
-      <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
           <t>KESİN</t>
@@ -15873,4 +15726,6666 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J141"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="120" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kod</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dönem</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Önceki FCF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Yeni FCF</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Önceki CAPEX</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Yeni CAPEX</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Önceki statü</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Yeni statü</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Kaynak</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Açıklama</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>13484.3667798</v>
+      </c>
+      <c r="D2" t="n">
+        <v>13484.3667798</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28724.300085</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28724.300085</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 14,362.2); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -37.0; duran varlık satışı ✗ +0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10087.8417163</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10087.8417163</v>
+      </c>
+      <c r="E3" t="n">
+        <v>27497.3504697</v>
+      </c>
+      <c r="F3" t="n">
+        <v>27497.3504697</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 13,748.7); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -35.2; duran varlık satışı ✗ +0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>13793.8132619</v>
+      </c>
+      <c r="D4" t="n">
+        <v>13793.8132619</v>
+      </c>
+      <c r="E4" t="n">
+        <v>24957.2042586</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24957.2042586</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 12,478.6); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -35.3; duran varlık satışı ✗ -0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>16194.0184064</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16194.0184064</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22505.2007424</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22505.2007424</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 11,252.6); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -33.8; duran varlık satışı ✗ +0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AGHOL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>17563.060965</v>
+      </c>
+      <c r="D6" t="n">
+        <v>17563.060965</v>
+      </c>
+      <c r="E6" t="n">
+        <v>45250.8359394</v>
+      </c>
+      <c r="F6" t="n">
+        <v>45250.8359394</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 22,625.4); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -42.7; duran varlık satışı ✗ +2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AGHOL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>13044.3543859</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13044.3543859</v>
+      </c>
+      <c r="E7" t="n">
+        <v>44789.5479527</v>
+      </c>
+      <c r="F7" t="n">
+        <v>44789.5479527</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 22,394.8); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -40.1; duran varlık satışı ✗ +2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AGHOL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>17409.0598865</v>
+      </c>
+      <c r="D8" t="n">
+        <v>17409.0598865</v>
+      </c>
+      <c r="E8" t="n">
+        <v>43182.2193634</v>
+      </c>
+      <c r="F8" t="n">
+        <v>43182.2193634</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 21,591.1); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -36.1; duran varlık satışı ✗ +0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AGHOL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>20688.7939584</v>
+      </c>
+      <c r="D9" t="n">
+        <v>20688.7939584</v>
+      </c>
+      <c r="E9" t="n">
+        <v>41328.8011264</v>
+      </c>
+      <c r="F9" t="n">
+        <v>41328.8011264</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 20,664.4); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -36.4; duran varlık satışı ✗ +1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AGROT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-191.2731996</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-191.2731996</v>
+      </c>
+      <c r="E10" t="n">
+        <v>302.3220924</v>
+      </c>
+      <c r="F10" t="n">
+        <v>302.3220924</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 151.2); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -285.4; duran varlık satışı ✗ +199.8; menkul kıymet/fon/türev ✗ -30.1; kur farkı (nakit dışı sunum) ✗ -10.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ALCAR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>-1844.9208268</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1844.9208268</v>
+      </c>
+      <c r="E11" t="n">
+        <v>120.7411837</v>
+      </c>
+      <c r="F11" t="n">
+        <v>120.7411837</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 170.9); kalemler (TTM, mn TL): duran varlık satışı ✗ +1,416.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ALCAR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-1814.645066</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-1814.645066</v>
+      </c>
+      <c r="E12" t="n">
+        <v>40.9963077</v>
+      </c>
+      <c r="F12" t="n">
+        <v>40.9963077</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 160.4); kalemler (TTM, mn TL): duran varlık satışı ✗ +1,380.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ALKIM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-639.9214584</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-639.9214584</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1245.087004</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1245.087004</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 250.5 ≤ eşik 622.5); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +395.2; SINIFLANMADI +250.5; alınan faiz ✗ +33.6; duran varlık satışı ✗ -31.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ARASE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7686.2650866</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2926.570353</v>
+      </c>
+      <c r="E14" t="n">
+        <v>20.6762664</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4780.371</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>KARMA (Diğer içindeki capex: BELGE dipnot; diğer bileşenler: BELGE)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 777.1); kalemler (TTM, mn TL): capex (dipnot: Diğer içindeki yatırım harcaması → CAPEX’e eklendi) -4,759.7; duran varlık satışı ✗ -3.9 'Diğer' içindeki yatırım harcaması (dipnot) CAPEX'e eklendi: +4,759.7 → |MDV+MODV alımı| içinde</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ARASE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>9766.9447189</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4856.8956884</v>
+      </c>
+      <c r="E15" t="n">
+        <v>21.5479695</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4931.597</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>KARMA (Diğer içindeki capex: BELGE dipnot; diğer bileşenler: BELGE)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 989.5); kalemler (TTM, mn TL): capex (dipnot: Diğer içindeki yatırım harcaması → CAPEX’e eklendi) -4,910.0 'Diğer' içindeki yatırım harcaması (dipnot) CAPEX'e eklendi: +4,910.0 → |MDV+MODV alımı| içinde</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ARASE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6811.0823066</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2345.7077265</v>
+      </c>
+      <c r="E16" t="n">
+        <v>22.6814199</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4488.056</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>KARMA (Diğer içindeki capex: BELGE dipnot; diğer bileşenler: BELGE)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 683.4); kalemler (TTM, mn TL): capex (dipnot: Diğer içindeki yatırım harcaması → CAPEX’e eklendi) -4,465.4 'Diğer' içindeki yatırım harcaması (dipnot) CAPEX'e eklendi: +4,465.4 → |MDV+MODV alımı| içinde</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ARASE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6862.2920704</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2418.6946576</v>
+      </c>
+      <c r="E17" t="n">
+        <v>21.2815872</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4464.879</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KARMA (Diğer içindeki capex: BELGE dipnot; diğer bileşenler: EVO (belgeyle teyitli))</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 701.6); kalemler (TTM, mn TL): capex (dipnot: Diğer içindeki yatırım harcaması → CAPEX’e eklendi) -4,443.6 'Diğer' içindeki yatırım harcaması (dipnot) CAPEX'e eklendi: +4,443.6 → |MDV+MODV alımı| içinde</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ARASE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>7707.3853537</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3334.6736886</v>
+      </c>
+      <c r="E18" t="n">
+        <v>25.1093349</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4397.821</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>KARMA (Diğer içindeki capex: BELGE dipnot; diğer bileşenler: EVO (belgeyle teyitli))</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 786.2); kalemler (TTM, mn TL): capex (dipnot: Diğer içindeki yatırım harcaması → CAPEX’e eklendi) -4,372.7 'Diğer' içindeki yatırım harcaması (dipnot) CAPEX'e eklendi: +4,372.7 → |MDV+MODV alımı| içinde</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ARASE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6966.1320704</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2708.4126576</v>
+      </c>
+      <c r="E19" t="n">
+        <v>29.3325872</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4287.052</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>KARMA (Diğer içindeki capex: BELGE dipnot; diğer bileşenler: EVO (belgeyle teyitli))</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 708.3); kalemler (TTM, mn TL): capex (dipnot: Diğer içindeki yatırım harcaması → CAPEX’e eklendi) -4,257.7 'Diğer' içindeki yatırım harcaması (dipnot) CAPEX'e eklendi: +4,257.7 → |MDV+MODV alımı| içinde</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ARSAN</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1089.7460268</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1089.7460268</v>
+      </c>
+      <c r="E20" t="n">
+        <v>63.9815158</v>
+      </c>
+      <c r="F20" t="n">
+        <v>63.9815158</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 116.9); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +436.1; iştirak/bağlı ortaklık (M&amp;A) ✗ -15.6; TMS 29 enflasyon etkisi ✗ +15.3; duran varlık satışı ✗ -9.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4797.418449</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4797.418449</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4571.7686514</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4571.7686514</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan -1,213.0 ≤ eşik 2,285.9); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -2,733.7; duran varlık satışı ✗ +2,577.9; SINIFLANMADI -1,213.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1459.0140604</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1459.0140604</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5453.1104514</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5453.1104514</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 2,726.6); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -3,661.4; duran varlık satışı ✗ +3,107.7; iştirak/bağlı ortaklık (M&amp;A) ✗ -367.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>-6592.1408181</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-6592.1408181</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5493.7426827</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5493.7426827</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 2,746.9); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -6,531.5; duran varlık satışı ✗ +3,889.5; iştirak/bağlı ortaklık (M&amp;A) ✗ -341.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>-2119.79776</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-2119.79776</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5366.3302656</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5366.3302656</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 2,683.2); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -5,376.7; duran varlık satışı ✗ +2,507.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>-2254.6699537</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-2254.6699537</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5773.9805802</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5773.9805802</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 2,887.0); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -5,549.2; duran varlık satışı ✗ +1,695.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>-306.497759999999</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-306.497759999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7097.1672656</v>
+      </c>
+      <c r="F26" t="n">
+        <v>7097.1672656</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 3,548.6); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -6,927.4; duran varlık satışı ✗ +1,318.8; iştirak/bağlı ortaklık (M&amp;A) ✗ +367.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ATATP</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2684.5259166</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2684.5259166</v>
+      </c>
+      <c r="E27" t="n">
+        <v>835.5087235</v>
+      </c>
+      <c r="F27" t="n">
+        <v>835.5087235</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 417.8); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -2,378.6; duran varlık satışı ✗ +2.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ATATP</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>97.1695622</v>
+      </c>
+      <c r="D28" t="n">
+        <v>97.1695622</v>
+      </c>
+      <c r="E28" t="n">
+        <v>973.7419271</v>
+      </c>
+      <c r="F28" t="n">
+        <v>973.7419271</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 486.9); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -839.6; duran varlık satışı ✗ +6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ATATP</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>-42.2193152000001</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-42.2193152000001</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1071.1826432</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1071.1826432</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 535.6); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -853.2; duran varlık satışı ✗ +102.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BESLR</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>-231.6025883</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-231.6025883</v>
+      </c>
+      <c r="E30" t="n">
+        <v>705.9089588000001</v>
+      </c>
+      <c r="F30" t="n">
+        <v>705.9089588000001</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 353.0); kalemler (TTM, mn TL): alınan faiz ✗ +3,886.5; kur farkı (nakit dışı sunum) ✗ +1,220.5; duran varlık satışı ✗ +36.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BESLR</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-2102.5388544</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-2102.5388544</v>
+      </c>
+      <c r="E31" t="n">
+        <v>866.9620736000001</v>
+      </c>
+      <c r="F31" t="n">
+        <v>866.9620736000001</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 433.5); kalemler (TTM, mn TL): alınan faiz ✗ +3,412.1; kur farkı (nakit dışı sunum) ✗ +1,305.4; duran varlık satışı ✗ +34.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BESLR</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>-1430.105136</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-1430.105136</v>
+      </c>
+      <c r="E32" t="n">
+        <v>932.4307916</v>
+      </c>
+      <c r="F32" t="n">
+        <v>932.4307916</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 466.2); kalemler (TTM, mn TL): alınan faiz ✗ +2,931.7; kur farkı (nakit dışı sunum) ✗ +1,396.1; duran varlık satışı ✗ +21.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BESLR</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>-733.3878544</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-733.3878544</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1054.5980736</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1054.5980736</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 527.3); kalemler (TTM, mn TL): alınan faiz ✗ +2,512.7; kur farkı (nakit dışı sunum) ✗ +1,307.4; duran varlık satışı ✗ +9.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BIENY</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-5638.8053358</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-5638.8053358</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3306.2436744</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3306.2436744</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 1,653.1); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +2,486.6; duran varlık satışı ✗ +5.8; alınan faiz ✗ -3.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BIENY</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>-3984.1362001</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-3984.1362001</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4109.8618928</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4109.8618928</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 5.8 ≤ eşik 2,054.9); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +1,499.9; duran varlık satışı ✗ +74.2; SINIFLANMADI +5.8; alınan faiz ✗ -4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BIENY</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>-5291.981897</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-5291.981897</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4228.5630758</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4228.5630758</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 9.4 ≤ eşik 2,114.3); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +760.0; alınan faiz ✗ -201.4; duran varlık satışı ✗ -10.4; SINIFLANMADI +9.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BOBET</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>-892.5128514</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-892.5128514</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2714.3483832</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2714.3483832</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 1,357.2); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -2,757.7; duran varlık satışı ✗ +1,112.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BOBET</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>-2395.7504094</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-2395.7504094</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2802.8950392</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2802.8950392</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 1,401.4); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -1,688.0; duran varlık satışı ✗ +1,507.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BOBET</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>-2150.536532</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-2150.536532</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2945.8658914</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2945.8658914</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 1,472.9); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -1,688.0; duran varlık satışı ✗ +1,293.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BOBET</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>-2906.2685184</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-2906.2685184</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3024.1969152</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3024.1969152</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 1,512.1); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -3,058.2; duran varlık satışı ✗ +1,857.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BOBET</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-1256.0384157</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-1256.0384157</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3750.1163718</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3750.1163718</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 1,875.1); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -3,058.2; duran varlık satışı ✗ +2,085.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BOBET</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>-2153.7485184</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-2153.7485184</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3994.9029152</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3994.9029152</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 1,997.5); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -3,058.2; duran varlık satışı ✗ +1,568.0; TMS 29 enflasyon etkisi ✗ +1,307.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BRLSM</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>146.3297163</v>
+      </c>
+      <c r="D43" t="n">
+        <v>146.3297163</v>
+      </c>
+      <c r="E43" t="n">
+        <v>11.1120143</v>
+      </c>
+      <c r="F43" t="n">
+        <v>11.1120143</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 15.7); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -379.1; duran varlık satışı ✗ +188.9; alınan faiz ✗ +44.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CEMTS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-248.0814592</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-248.0814592</v>
+      </c>
+      <c r="E44" t="n">
+        <v>334.7881472</v>
+      </c>
+      <c r="F44" t="n">
+        <v>334.7881472</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 167.4); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -295.3; alınan faiz ✗ +287.5; duran varlık satışı ✗ +2.2; iştirak/bağlı ortaklık (M&amp;A) ✗ -0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CEMTS</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.437494700000002</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.437494700000002</v>
+      </c>
+      <c r="E45" t="n">
+        <v>298.6144868</v>
+      </c>
+      <c r="F45" t="n">
+        <v>298.6144868</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 149.3); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -240.9; alınan faiz ✗ +201.0; duran varlık satışı ✗ +5.2; iştirak/bağlı ortaklık (M&amp;A) ✗ -0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CIMSA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2572.0585572</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2572.0585572</v>
+      </c>
+      <c r="E46" t="n">
+        <v>6757.8195834</v>
+      </c>
+      <c r="F46" t="n">
+        <v>6757.8195834</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan -3.1 ≤ eşik 3,378.9); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -14.2; SINIFLANMADI -3.1; alınan temettü (FCF_HLD’de) +0.2; duran varlık satışı ✗ -0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CIMSA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1730.4657762</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1730.4657762</v>
+      </c>
+      <c r="E47" t="n">
+        <v>7401.2529083</v>
+      </c>
+      <c r="F47" t="n">
+        <v>7401.2529083</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan -4.8 ≤ eşik 3,700.6); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -14.2; SINIFLANMADI -4.8; verilen avans/borç ✗ +0.4; alınan temettü (FCF_HLD’de) +0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CIMSA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>-2679.1951287</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-2679.1951287</v>
+      </c>
+      <c r="E48" t="n">
+        <v>7721.6147208</v>
+      </c>
+      <c r="F48" t="n">
+        <v>7721.6147208</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan -1,701.0 ≤ eşik 3,860.8); kalemler (TTM, mn TL): SINIFLANMADI -1,701.0; duran varlık satışı ✗ -251.1; verilen avans/borç ✗ +155.6; alınan temettü (FCF_HLD’de) -41.2; iştirak/bağlı ortaklık (M&amp;A) ✗ -14.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CWENE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-10106.1584796</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-10106.1584796</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2659.5486648</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2659.5486648</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 1,080.7 ≤ eşik 1,329.8); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +3,188.0; SINIFLANMADI +1,080.7; duran varlık satışı ✗ +274.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CWENE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>-9073.311846500001</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-9073.311846500001</v>
+      </c>
+      <c r="E50" t="n">
+        <v>6011.9633091</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6011.9633091</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 1,080.7 ≤ eşik 3,006.0); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +2,979.1; SINIFLANMADI +1,080.7; duran varlık satışı ✗ +220.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DGNMO</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>354.0259105</v>
+      </c>
+      <c r="D51" t="n">
+        <v>354.0259105</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1076.0021647</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1076.0021647</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 538.0); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +561.2; duran varlık satışı ✗ +65.6; alınan faiz ✗ -17.0 · NOT: DGNMO 2025/06 şirket sitesi konsolide raporu: A 524.522.345, A+B+C(+etki) = net değişim ✓. Evo 2024/06 ve 2024/12 değerleri belgelerle birebir; yalnız Evo 2025/06 CFO (−1.404,8 mn) belgeyle uyuşmuyor → Evo hatası.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DGNMO</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1508.2966251</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1508.2966251</v>
+      </c>
+      <c r="E52" t="n">
+        <v>701.7087036</v>
+      </c>
+      <c r="F52" t="n">
+        <v>701.7087036</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 350.9); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +147.8; duran varlık satışı ✗ +83.2; alınan faiz ✗ -50.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DOFER</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-344.1013598</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-344.1013598</v>
+      </c>
+      <c r="E53" t="n">
+        <v>29.1236495</v>
+      </c>
+      <c r="F53" t="n">
+        <v>29.1236495</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 31.5); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -78.6; duran varlık satışı ✗ -8.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DOFER</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>-685.5109661</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-685.5109661</v>
+      </c>
+      <c r="E54" t="n">
+        <v>56.418799</v>
+      </c>
+      <c r="F54" t="n">
+        <v>56.418799</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 62.9); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -44.0; duran varlık satışı ✗ +4.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DOFER</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>-458.7317248</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-458.7317248</v>
+      </c>
+      <c r="E55" t="n">
+        <v>151.5488768</v>
+      </c>
+      <c r="F55" t="n">
+        <v>151.5488768</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 75.8); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -134.5; duran varlık satışı ✗ +9.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DOFER</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>-200.6995819</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-200.6995819</v>
+      </c>
+      <c r="E56" t="n">
+        <v>194.2554977</v>
+      </c>
+      <c r="F56" t="n">
+        <v>194.2554977</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 97.1); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -134.5; duran varlık satışı ✗ +22.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ECILC</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1170.2823936</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1170.2823936</v>
+      </c>
+      <c r="E57" t="n">
+        <v>389.2285952</v>
+      </c>
+      <c r="F57" t="n">
+        <v>389.2285952</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 194.6); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +4,114.0; alınan temettü (FCF_HLD’de) +953.5; duran varlık satışı ✗ +343.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>EGEEN</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1045.73824</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1045.73824</v>
+      </c>
+      <c r="E58" t="n">
+        <v>485.106432</v>
+      </c>
+      <c r="F58" t="n">
+        <v>485.106432</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.6 ≤ eşik 242.6); kalemler (TTM, mn TL): SINIFLANMADI +0.6; alınan faiz ✗ +0.3; verilen avans/borç ✗ -0.1; duran varlık satışı ✗ +0.1; alınan temettü (FCF_HLD’de) +0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>EGEEN</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>628.3040011000001</v>
+      </c>
+      <c r="D59" t="n">
+        <v>628.3040011000001</v>
+      </c>
+      <c r="E59" t="n">
+        <v>436.641603</v>
+      </c>
+      <c r="F59" t="n">
+        <v>436.641603</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.6 ≤ eşik 218.3); kalemler (TTM, mn TL): SINIFLANMADI +0.6; alınan faiz ✗ +0.3; verilen avans/borç ✗ -0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>EGEEN</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>274.68024</v>
+      </c>
+      <c r="D60" t="n">
+        <v>274.68024</v>
+      </c>
+      <c r="E60" t="n">
+        <v>353.593432</v>
+      </c>
+      <c r="F60" t="n">
+        <v>353.593432</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.6 ≤ eşik 176.8); kalemler (TTM, mn TL): SINIFLANMADI +0.6; alınan faiz ✗ +0.3; menkul kıymet/fon/türev ✗ -0.2; verilen avans/borç ✗ -0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ENDAE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>-377.3453064</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-377.3453064</v>
+      </c>
+      <c r="E61" t="n">
+        <v>61.0650468</v>
+      </c>
+      <c r="F61" t="n">
+        <v>61.0650468</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 30.5); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +751.1; verilen avans/borç ✗ -353.2; iştirak/bağlı ortaklık (M&amp;A) ✗ -321.1; duran varlık satışı ✗ -0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ESEN</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1856.7408977</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1856.7408977</v>
+      </c>
+      <c r="E62" t="n">
+        <v>111.1968843</v>
+      </c>
+      <c r="F62" t="n">
+        <v>111.1968843</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 197.2); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -393.8; geri alınan paylar (finansman niteliğinde) ✗ -220.4; duran varlık satışı ✗ +118.5; alınan faiz ✗ +58.4; alınan temettü (FCF_HLD’de) +16.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ESEN</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>676.5564916</v>
+      </c>
+      <c r="D63" t="n">
+        <v>676.5564916</v>
+      </c>
+      <c r="E63" t="n">
+        <v>45.2859707</v>
+      </c>
+      <c r="F63" t="n">
+        <v>45.2859707</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 72.2); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -393.8; alınan faiz ✗ +265.9; geri alınan paylar (finansman niteliğinde) ✗ -206.4; duran varlık satışı ✗ +46.5; alınan temettü (FCF_HLD’de) +16.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ESEN</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>623.5868713999999</v>
+      </c>
+      <c r="D64" t="n">
+        <v>623.5868713999999</v>
+      </c>
+      <c r="E64" t="n">
+        <v>114.6037772</v>
+      </c>
+      <c r="F64" t="n">
+        <v>114.6037772</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 73.8); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ +141.1; geri alınan paylar (finansman niteliğinde) ✗ -109.6; duran varlık satışı ✗ +18.6; alınan faiz ✗ -6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>GENIL</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>642.5466622</v>
+      </c>
+      <c r="D65" t="n">
+        <v>642.5466622</v>
+      </c>
+      <c r="E65" t="n">
+        <v>833.618029</v>
+      </c>
+      <c r="F65" t="n">
+        <v>833.618029</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 416.8); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -1,681.8; duran varlık satışı ✗ +887.7; alınan faiz ✗ +482.3; iştirak/bağlı ortaklık (M&amp;A) ✗ -47.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>GENIL</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>590.6040832</v>
+      </c>
+      <c r="D66" t="n">
+        <v>590.6040832</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1159.2518144</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1159.2518144</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 579.6); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -2,728.6; alınan faiz ✗ +642.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>GENIL</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>679.2479569</v>
+      </c>
+      <c r="D67" t="n">
+        <v>679.2479569</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1166.6108921</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1166.6108921</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 583.3); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -2,594.9; alınan faiz ✗ +642.1; iştirak/bağlı ortaklık (M&amp;A) ✗ -141.4; duran varlık satışı ✗ +0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>GENIL</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>452.8670832</v>
+      </c>
+      <c r="D68" t="n">
+        <v>452.8670832</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1101.2358144</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1101.2358144</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 550.6); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -2,545.3; alınan faiz ✗ +563.7; iştirak/bağlı ortaklık (M&amp;A) ✗ -437.2; duran varlık satışı ✗ +25.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>GIPTA</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>-48.3529657</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-48.3529657</v>
+      </c>
+      <c r="E69" t="n">
+        <v>46.2632459</v>
+      </c>
+      <c r="F69" t="n">
+        <v>46.2632459</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 23.1); kalemler (TTM, mn TL): alınan faiz ✗ +647.2; menkul kıymet/fon/türev ✗ +23.5; duran varlık satışı ✗ +13.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>GIPTA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>573.1501444</v>
+      </c>
+      <c r="D70" t="n">
+        <v>573.1501444</v>
+      </c>
+      <c r="E70" t="n">
+        <v>63.1806552</v>
+      </c>
+      <c r="F70" t="n">
+        <v>63.1806552</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 63.6); kalemler (TTM, mn TL): alınan faiz ✗ +652.2; menkul kıymet/fon/türev ✗ -532.3; duran varlık satışı ✗ +10.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>GIPTA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>109.520648</v>
+      </c>
+      <c r="D71" t="n">
+        <v>109.520648</v>
+      </c>
+      <c r="E71" t="n">
+        <v>40.0700752</v>
+      </c>
+      <c r="F71" t="n">
+        <v>40.0700752</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 20.0); kalemler (TTM, mn TL): alınan faiz ✗ +520.1; menkul kıymet/fon/türev ✗ +192.3; duran varlık satışı ✗ +15.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>GOKNR</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>157.5722051</v>
+      </c>
+      <c r="D72" t="n">
+        <v>157.5722051</v>
+      </c>
+      <c r="E72" t="n">
+        <v>536.1667416</v>
+      </c>
+      <c r="F72" t="n">
+        <v>536.1667416</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 268.1); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -1,775.6; duran varlık satışı ✗ +263.4; alınan faiz ✗ +112.3; TMS 29 enflasyon etkisi ✗ +91.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>GOKNR</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>726.6453125</v>
+      </c>
+      <c r="D73" t="n">
+        <v>726.6453125</v>
+      </c>
+      <c r="E73" t="n">
+        <v>383.6995764</v>
+      </c>
+      <c r="F73" t="n">
+        <v>383.6995764</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 191.8); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +448.7; TMS 29 enflasyon etkisi ✗ -130.0; alınan faiz ✗ +113.6; duran varlık satışı ✗ +3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>GOKNR</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1531.1472896</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1531.1472896</v>
+      </c>
+      <c r="E74" t="n">
+        <v>537.7400720000001</v>
+      </c>
+      <c r="F74" t="n">
+        <v>537.7400720000001</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 268.9); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +2,031.9; alınan faiz ✗ +281.3; duran varlık satışı ✗ +119.2; TMS 29 enflasyon etkisi ✗ +59.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>GUBRF</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6202.4395103</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6202.4395103</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2821.4227629</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2821.4227629</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 1,041.8 ≤ eşik 1,410.7); kalemler (TTM, mn TL): SINIFLANMADI +1,041.8; duran varlık satışı ✗ +176.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>GZNMI</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>-411.1516452</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-411.1516452</v>
+      </c>
+      <c r="E76" t="n">
+        <v>39.5561406</v>
+      </c>
+      <c r="F76" t="n">
+        <v>39.5561406</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 19.8); kalemler (TTM, mn TL): alınan faiz ✗ +98.8; menkul kıymet/fon/türev ✗ -73.6; duran varlık satışı ✗ +2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>KCHOL</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>115945.715</v>
+      </c>
+      <c r="D77" t="n">
+        <v>115945.715</v>
+      </c>
+      <c r="E77" t="n">
+        <v>146390.295</v>
+      </c>
+      <c r="F77" t="n">
+        <v>146390.295</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.1 ≤ eşik 73,195.1); kalemler (TTM, mn TL): SINIFLANMADI +0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>KCHOL</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>-252716.4928</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-252716.4928</v>
+      </c>
+      <c r="E78" t="n">
+        <v>121182.1056</v>
+      </c>
+      <c r="F78" t="n">
+        <v>121182.1056</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan -0.1 ≤ eşik 60,591.1); kalemler (TTM, mn TL): SINIFLANMADI -0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>KCHOL</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>-148063.9229</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-148063.9229</v>
+      </c>
+      <c r="E79" t="n">
+        <v>117157.4595</v>
+      </c>
+      <c r="F79" t="n">
+        <v>117157.4595</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan -0.2 ≤ eşik 58,578.7); kalemler (TTM, mn TL): SINIFLANMADI -0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>KCHOL</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>-192410.4928</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-192410.4928</v>
+      </c>
+      <c r="E80" t="n">
+        <v>118577.1056</v>
+      </c>
+      <c r="F80" t="n">
+        <v>118577.1056</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan -0.1 ≤ eşik 59,288.6); kalemler (TTM, mn TL): SINIFLANMADI -0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MAGEN</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>87.0073266</v>
+      </c>
+      <c r="D81" t="n">
+        <v>87.0073266</v>
+      </c>
+      <c r="E81" t="n">
+        <v>105.4748754</v>
+      </c>
+      <c r="F81" t="n">
+        <v>105.4748754</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 52.7); kalemler (TTM, mn TL): geri alınan paylar (finansman niteliğinde) ✗ +240.4; duran varlık satışı ✗ +49.3; alınan faiz ✗ +22.9; alınan temettü (FCF_HLD’de) +16.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MAGEN</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>643.0752063</v>
+      </c>
+      <c r="D82" t="n">
+        <v>643.0752063</v>
+      </c>
+      <c r="E82" t="n">
+        <v>41.0312633</v>
+      </c>
+      <c r="F82" t="n">
+        <v>41.0312633</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 68.4); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -393.8; geri alınan paylar (finansman niteliğinde) ✗ -107.2; alınan faiz ✗ +54.3; duran varlık satışı ✗ +51.4; alınan temettü (FCF_HLD’de) +16.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MAKIM</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.179142599999995</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-0.179142599999995</v>
+      </c>
+      <c r="E83" t="n">
+        <v>76.70167189999999</v>
+      </c>
+      <c r="F83" t="n">
+        <v>76.70167189999999</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 38.4); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -39.6; duran varlık satışı ✗ +6.6; iştirak/bağlı ortaklık (M&amp;A) ✗ -0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MEGMT</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>-496.056</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-496.056</v>
+      </c>
+      <c r="E84" t="n">
+        <v>190.013</v>
+      </c>
+      <c r="F84" t="n">
+        <v>190.013</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan -6.3 ≤ eşik 95.0); kalemler (TTM, mn TL): duran varlık satışı ✗ -207.1; SINIFLANMADI -6.3; menkul kıymet/fon/türev ✗ -3.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>NATEN</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>507.1079503</v>
+      </c>
+      <c r="D85" t="n">
+        <v>507.1079503</v>
+      </c>
+      <c r="E85" t="n">
+        <v>144.7294814</v>
+      </c>
+      <c r="F85" t="n">
+        <v>144.7294814</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 72.4); kalemler (TTM, mn TL): alınan faiz ✗ +267.7; iştirak/bağlı ortaklık (M&amp;A) ✗ +141.1; geri alınan paylar (finansman niteliğinde) ✗ -126.4; duran varlık satışı ✗ +72.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>NETAS</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>-271.71</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-271.71</v>
+      </c>
+      <c r="E86" t="n">
+        <v>12.163</v>
+      </c>
+      <c r="F86" t="n">
+        <v>12.163</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 8.4); kalemler (TTM, mn TL): kur farkı (nakit dışı sunum) ✗ -10.2; duran varlık satışı ✗ +3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>OYAKC</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>3487.4648624</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3487.4648624</v>
+      </c>
+      <c r="E87" t="n">
+        <v>8047.754448</v>
+      </c>
+      <c r="F87" t="n">
+        <v>8047.754448</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 4,023.9); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +2,630.2; alınan faiz ✗ +852.4; duran varlık satışı ✗ +19.5; alınan temettü (FCF_HLD’de) +4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PGSUS</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>11073.452</v>
+      </c>
+      <c r="D88" t="n">
+        <v>11073.452</v>
+      </c>
+      <c r="E88" t="n">
+        <v>3205.517</v>
+      </c>
+      <c r="F88" t="n">
+        <v>3205.517</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan -1,061.7 ≤ eşik 3,415.7); kalemler (TTM, mn TL): verilen avans/borç ✗ -12,082.0; menkul kıymet/fon/türev ✗ -2,295.6; alınan faiz ✗ +2,133.1; SINIFLANMADI -1,061.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>PKART</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>-290.8851006</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-290.8851006</v>
+      </c>
+      <c r="E89" t="n">
+        <v>99.3576216</v>
+      </c>
+      <c r="F89" t="n">
+        <v>99.3576216</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 49.7); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +696.5; duran varlık satışı ✗ +1.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>PKART</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>-278.97723</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-278.97723</v>
+      </c>
+      <c r="E90" t="n">
+        <v>65.7646763</v>
+      </c>
+      <c r="F90" t="n">
+        <v>65.7646763</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 32.9); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +192.7; duran varlık satışı ✗ +1.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>PKART</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>-219.3792711</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-219.3792711</v>
+      </c>
+      <c r="E91" t="n">
+        <v>33.8428592</v>
+      </c>
+      <c r="F91" t="n">
+        <v>33.8428592</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 18.6); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +116.2; duran varlık satışı ✗ +0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>PNLSN</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>-233.5435319</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-233.5435319</v>
+      </c>
+      <c r="E92" t="n">
+        <v>411.8014288</v>
+      </c>
+      <c r="F92" t="n">
+        <v>411.8014288</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 205.9); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +439.4; duran varlık satışı ✗ +5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>PNLSN</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>-121.3232365</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-121.3232365</v>
+      </c>
+      <c r="E93" t="n">
+        <v>353.6613889</v>
+      </c>
+      <c r="F93" t="n">
+        <v>353.6613889</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 176.8); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +355.3; duran varlık satışı ✗ +4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PNLSN</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>-101.4655488</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-101.4655488</v>
+      </c>
+      <c r="E94" t="n">
+        <v>231.9024128</v>
+      </c>
+      <c r="F94" t="n">
+        <v>231.9024128</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 116.0); kalemler (TTM, mn TL): duran varlık satışı ✗ +23.2; iştirak/bağlı ortaklık (M&amp;A) ✗ -7.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>PNLSN</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>-88.42638030000001</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-88.42638030000001</v>
+      </c>
+      <c r="E95" t="n">
+        <v>197.6838251</v>
+      </c>
+      <c r="F95" t="n">
+        <v>197.6838251</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 98.8); kalemler (TTM, mn TL): duran varlık satışı ✗ +47.1; menkul kıymet/fon/türev ✗ -24.7; iştirak/bağlı ortaklık (M&amp;A) ✗ -15.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>PNLSN</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>-110.1465488</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-110.1465488</v>
+      </c>
+      <c r="E96" t="n">
+        <v>60.3134128</v>
+      </c>
+      <c r="F96" t="n">
+        <v>60.3134128</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 30.2); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -178.9; duran varlık satışı ✗ +32.1; iştirak/bağlı ortaklık (M&amp;A) ✗ -16.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>PRKAB</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>-114.453039699999</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-114.453039699999</v>
+      </c>
+      <c r="E97" t="n">
+        <v>65.2200838</v>
+      </c>
+      <c r="F97" t="n">
+        <v>65.2200838</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 32.6); kalemler (TTM, mn TL): alınan faiz ✗ +161.9; duran varlık satışı ✗ +10.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>QUAGR</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>3296.1954834</v>
+      </c>
+      <c r="D98" t="n">
+        <v>3296.1954834</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan -128.9 ≤ eşik 337.2); kalemler (TTM, mn TL): duran varlık satışı ✗ -1,970.3; menkul kıymet/fon/türev ✗ +929.4; alınan faiz ✗ +697.8; SINIFLANMADI -128.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SAHOL</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>-91648.091539</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-91648.091539</v>
+      </c>
+      <c r="E99" t="n">
+        <v>42889.7309214</v>
+      </c>
+      <c r="F99" t="n">
+        <v>42889.7309214</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 21,444.9); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +70.9; iştirak/bağlı ortaklık (M&amp;A) ✗ -16.2; alınan temettü (FCF_HLD’de) +11.2; duran varlık satışı ✗ +1.4 · NOT: SAHOL 2024 nakit akışını 31.12.2025 raporunda işletme↔yatırım arasında yeniden sınıflamış (2024 işletme: orijinal (90,8) mlr, düzenlenmiş +153,2 mlr; net değişim aynı). 2025/03–09 raporlarının karşılaştırmalı sütunları eski esasta (Evo 2024/03-06-09 bunlarla aynı) → tutarlı TTM orijinal 2024 raporuyla kurulur. Evo 2024/12’yi yeni esastan (+180,4 mlr) almış; V7 TTM iki esası karıştırıyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SAHOL</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>-131133.3860922</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-131133.3860922</v>
+      </c>
+      <c r="E100" t="n">
+        <v>43298.2201859</v>
+      </c>
+      <c r="F100" t="n">
+        <v>43298.2201859</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 21,649.1); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -18.2; menkul kıymet/fon/türev ✗ -15.5; alınan temettü (FCF_HLD’de) +7.2; duran varlık satışı ✗ +1.6 · NOT: SAHOL 2024 nakit akışını 31.12.2025 raporunda işletme↔yatırım arasında yeniden sınıflamış (2024 işletme: orijinal (90,8) mlr, düzenlenmiş +153,2 mlr; net değişim aynı). 2025/03–09 raporlarının karşılaştırmalı sütunları eski esasta (Evo 2024/03-06-09 bunlarla aynı) → tutarlı TTM orijinal 2024 raporuyla kurulur. Evo 2024/12’yi yeni esastan (+180,4 mlr) almış; V7 TTM iki esası karıştırıyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SAHOL</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>-160615.6380749</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-160615.6380749</v>
+      </c>
+      <c r="E101" t="n">
+        <v>39765.5184303</v>
+      </c>
+      <c r="F101" t="n">
+        <v>39765.5184303</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan -98.9 ≤ eşik 19,882.8); kalemler (TTM, mn TL): SINIFLANMADI -98.9; menkul kıymet/fon/türev ✗ +67.0; iştirak/bağlı ortaklık (M&amp;A) ✗ -15.9; alınan temettü (FCF_HLD’de) +6.6; duran varlık satışı ✗ +2.5 · NOT: SAHOL 2024 nakit akışını 31.12.2025 raporunda işletme↔yatırım arasında yeniden sınıflamış (2024 işletme: orijinal (90,8) mlr, düzenlenmiş +153,2 mlr; net değişim aynı). 2025/03–09 raporlarının karşılaştırmalı sütunları eski esasta (Evo 2024/03-06-09 bunlarla aynı) → tutarlı TTM orijinal 2024 raporuyla kurulur. Evo 2024/12’yi yeni esastan (+180,4 mlr) almış; V7 TTM iki esası karıştırıyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SAHOL</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>59655.1213104</v>
+      </c>
+      <c r="D102" t="n">
+        <v>59655.1213104</v>
+      </c>
+      <c r="E102" t="n">
+        <v>41739.6504576</v>
+      </c>
+      <c r="F102" t="n">
+        <v>41739.6504576</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 20,869.8); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -258.6; alınan temettü (FCF_HLD’de) +5.3; duran varlık satışı ✗ +2.2; iştirak/bağlı ortaklık (M&amp;A) ✗ -1.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SAHOL</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>-73812.3594934</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-73812.3594934</v>
+      </c>
+      <c r="E103" t="n">
+        <v>43226.8162761</v>
+      </c>
+      <c r="F103" t="n">
+        <v>43226.8162761</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 21,613.4); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -186.9; duran varlık satışı ✗ +2.4; iştirak/bağlı ortaklık (M&amp;A) ✗ -1.8; alınan temettü (FCF_HLD’de) +0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SAHOL</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>-49369.3456896</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-49369.3456896</v>
+      </c>
+      <c r="E104" t="n">
+        <v>41146.9644576</v>
+      </c>
+      <c r="F104" t="n">
+        <v>41146.9644576</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 20,573.5); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -158.7; iştirak/bağlı ortaklık (M&amp;A) ✗ +18.8; alınan temettü (FCF_HLD’de) +3.9; duran varlık satışı ✗ +3.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SAYAS</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>-62.3229167000001</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-62.3229167000001</v>
+      </c>
+      <c r="E105" t="n">
+        <v>413.22593</v>
+      </c>
+      <c r="F105" t="n">
+        <v>413.22593</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 206.6); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +242.8; alınan faiz ✗ +46.5; duran varlık satışı ✗ +5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SAYAS</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>48.6935176999999</v>
+      </c>
+      <c r="D106" t="n">
+        <v>48.6935176999999</v>
+      </c>
+      <c r="E106" t="n">
+        <v>265.4743744</v>
+      </c>
+      <c r="F106" t="n">
+        <v>265.4743744</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 132.7); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +232.4; alınan faiz ✗ +46.5; duran varlık satışı ✗ +6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SAYAS</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>-193.2841984</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-193.2841984</v>
+      </c>
+      <c r="E107" t="n">
+        <v>197.4046208</v>
+      </c>
+      <c r="F107" t="n">
+        <v>197.4046208</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 98.7); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +256.4; duran varlık satışı ✗ +5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SAYAS</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>-298.9726249</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-298.9726249</v>
+      </c>
+      <c r="E108" t="n">
+        <v>24.1490102</v>
+      </c>
+      <c r="F108" t="n">
+        <v>24.1490102</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 27.5); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +236.4; duran varlık satışı ✗ +2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SAYAS</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>184.9158016</v>
+      </c>
+      <c r="D109" t="n">
+        <v>184.9158016</v>
+      </c>
+      <c r="E109" t="n">
+        <v>19.1686208</v>
+      </c>
+      <c r="F109" t="n">
+        <v>19.1686208</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 20.4); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -85.7; duran varlık satışı ✗ +2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SDTTR</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>51.7733256999999</v>
+      </c>
+      <c r="D110" t="n">
+        <v>51.7733256999999</v>
+      </c>
+      <c r="E110" t="n">
+        <v>281.7027357</v>
+      </c>
+      <c r="F110" t="n">
+        <v>281.7027357</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 140.9); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -309.7; duran varlık satışı ✗ +0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SDTTR</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>-4.51020799999998</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-4.51020799999998</v>
+      </c>
+      <c r="E111" t="n">
+        <v>412.1917952</v>
+      </c>
+      <c r="F111" t="n">
+        <v>412.1917952</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 206.1); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -354.4; duran varlık satışı ✗ +37.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SDTTR</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>-225.7373315</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-225.7373315</v>
+      </c>
+      <c r="E112" t="n">
+        <v>670.7054831</v>
+      </c>
+      <c r="F112" t="n">
+        <v>670.7054831</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 335.4); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -354.4; duran varlık satışı ✗ +37.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SNPAM</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>264.0627438</v>
+      </c>
+      <c r="D113" t="n">
+        <v>264.0627438</v>
+      </c>
+      <c r="E113" t="n">
+        <v>58.929465</v>
+      </c>
+      <c r="F113" t="n">
+        <v>58.929465</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 32.3); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -172.2; duran varlık satışı ✗ +17.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SNPAM</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>498.679297</v>
+      </c>
+      <c r="D114" t="n">
+        <v>498.679297</v>
+      </c>
+      <c r="E114" t="n">
+        <v>112.9296013</v>
+      </c>
+      <c r="F114" t="n">
+        <v>112.9296013</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 61.2); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -352.8; menkul kıymet/fon/türev ✗ -189.4; alınan faiz ✗ +29.3; duran varlık satışı ✗ +0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SONME</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>14.5436639</v>
+      </c>
+      <c r="D115" t="n">
+        <v>14.5436639</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.3060048</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.3060048</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 1.5); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -47.4; alınan faiz ✗ +43.8; menkul kıymet/fon/türev ✗ +25.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SONME</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>109.0904208</v>
+      </c>
+      <c r="D116" t="n">
+        <v>109.0904208</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.1539104</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.1539104</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 10.9); kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ -127.4; alınan faiz ✗ +43.8; menkul kıymet/fon/türev ✗ +23.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SUNTK</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>-568.6507183</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-568.6507183</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1311.3635922</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1311.3635922</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan -14.3 ≤ eşik 655.7); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +667.7; duran varlık satışı ✗ +37.5; SINIFLANMADI -14.3; verilen avans/borç ✗ -7.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SUNTK</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>-647.4303488</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-647.4303488</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1287.9623168</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1287.9623168</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 644.0); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +714.9; verilen avans/borç ✗ +94.6; duran varlık satışı ✗ +12.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SUNTK</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>-79.7198266999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-79.7198266999999</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1135.4463143</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1135.4463143</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 567.7); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +756.8; verilen avans/borç ✗ +65.8; duran varlık satışı ✗ +15.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>SUNTK</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>699.0246512</v>
+      </c>
+      <c r="D120" t="n">
+        <v>699.0246512</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1008.6313168</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1008.6313168</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 504.3); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +728.7; verilen avans/borç ✗ +94.6; duran varlık satışı ✗ +42.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>TEZOL</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>261.6256428</v>
+      </c>
+      <c r="D121" t="n">
+        <v>261.6256428</v>
+      </c>
+      <c r="E121" t="n">
+        <v>243.8376042</v>
+      </c>
+      <c r="F121" t="n">
+        <v>243.8376042</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 121.9); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -466.2; verilen avans/borç ✗ +369.7; alınan faiz ✗ +195.4; duran varlık satışı ✗ +4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>TEZOL</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1243.8725563</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1243.8725563</v>
+      </c>
+      <c r="E122" t="n">
+        <v>190.5943242</v>
+      </c>
+      <c r="F122" t="n">
+        <v>190.5943242</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 147.0); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +268.3; alınan faiz ✗ +204.4; duran varlık satışı ✗ +103.9; verilen avans/borç ✗ +47.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>TEZOL</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>1049.9058301</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1049.9058301</v>
+      </c>
+      <c r="E123" t="n">
+        <v>118.8641333</v>
+      </c>
+      <c r="F123" t="n">
+        <v>118.8641333</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 120.3); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -466.6; verilen avans/borç ✗ +369.5; alınan faiz ✗ +195.5; duran varlık satışı ✗ +4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>TEZOL</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>984.0685056</v>
+      </c>
+      <c r="D124" t="n">
+        <v>984.0685056</v>
+      </c>
+      <c r="E124" t="n">
+        <v>102.8645376</v>
+      </c>
+      <c r="F124" t="n">
+        <v>102.8645376</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.4 ≤ eşik 110.0); kalemler (TTM, mn TL): SINIFLANMADI +0.4; alınan faiz ✗ +0.4; duran varlık satışı ✗ +0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>TEZOL</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>711.3931143</v>
+      </c>
+      <c r="D125" t="n">
+        <v>711.3931143</v>
+      </c>
+      <c r="E125" t="n">
+        <v>77.9718714</v>
+      </c>
+      <c r="F125" t="n">
+        <v>77.9718714</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.4 ≤ eşik 79.9); kalemler (TTM, mn TL): alınan faiz ✗ +0.4; SINIFLANMADI +0.4; menkul kıymet/fon/türev ✗ -0.2; duran varlık satışı ✗ +0.1; verilen avans/borç ✗ -0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>TEZOL</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>183.9275056</v>
+      </c>
+      <c r="D126" t="n">
+        <v>183.9275056</v>
+      </c>
+      <c r="E126" t="n">
+        <v>127.4685376</v>
+      </c>
+      <c r="F126" t="n">
+        <v>127.4685376</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.4 ≤ eşik 63.7); kalemler (TTM, mn TL): alınan faiz ✗ +0.4; SINIFLANMADI +0.4; menkul kıymet/fon/türev ✗ -0.2; verilen avans/borç ✗ -0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>TRALT</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>-5761.8431094</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-5761.8431094</v>
+      </c>
+      <c r="E127" t="n">
+        <v>9106.7962056</v>
+      </c>
+      <c r="F127" t="n">
+        <v>9106.7962056</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 5.5 ≤ eşik 4,553.4); kalemler (TTM, mn TL): SINIFLANMADI +5.5; alınan faiz ✗ +1.7; verilen avans/borç ✗ +0.9; menkul kıymet/fon/türev ✗ -0.9; duran varlık satışı ✗ +0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>TRALT</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>-4372.6815106</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-4372.6815106</v>
+      </c>
+      <c r="E128" t="n">
+        <v>7259.9472583</v>
+      </c>
+      <c r="F128" t="n">
+        <v>7259.9472583</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 5.5 ≤ eşik 3,630.0); kalemler (TTM, mn TL): SINIFLANMADI +5.5; alınan faiz ✗ +1.7; verilen avans/borç ✗ +0.7; menkul kıymet/fon/türev ✗ -0.1; duran varlık satışı ✗ +0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>UNLU</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>183.9417074</v>
+      </c>
+      <c r="D129" t="n">
+        <v>123.7338908</v>
+      </c>
+      <c r="E129" t="n">
+        <v>26.1141834</v>
+      </c>
+      <c r="F129" t="n">
+        <v>86.322</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>KARMA (Diğer içindeki capex: BELGE dipnot; diğer bileşenler: EVO (belgeyle teyitli))</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 20.5); kalemler (TTM, mn TL): capex (dipnot: Diğer içindeki yatırım harcaması → CAPEX’e eklendi) -60.2; alınan temettü (FCF_HLD’de) +5.3 'Diğer' içindeki yatırım harcaması (dipnot) CAPEX'e eklendi: +60.2 → |MDV+MODV alımı| içinde</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>UNLU</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>366.8213682</v>
+      </c>
+      <c r="D130" t="n">
+        <v>291.198912</v>
+      </c>
+      <c r="E130" t="n">
+        <v>23.9145438</v>
+      </c>
+      <c r="F130" t="n">
+        <v>99.53700000000001</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>KARMA (Diğer içindeki capex: BELGE dipnot; diğer bileşenler: EVO (belgeyle teyitli))</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 39.9); kalemler (TTM, mn TL): capex (dipnot: Diğer içindeki yatırım harcaması → CAPEX’e eklendi) -75.6; alınan temettü (FCF_HLD’de) +4.5 'Diğer' içindeki yatırım harcaması (dipnot) CAPEX'e eklendi: +75.6 → |MDV+MODV alımı| içinde</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>UNLU</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>-270.7670128</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-345.5221664</v>
+      </c>
+      <c r="E131" t="n">
+        <v>25.5998464</v>
+      </c>
+      <c r="F131" t="n">
+        <v>100.355</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>KARMA (Diğer içindeki capex: BELGE dipnot; diğer bileşenler: EVO (belgeyle teyitli))</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 23.1); kalemler (TTM, mn TL): alınan faiz ✗ +337.3; capex (dipnot: Diğer içindeki yatırım harcaması → CAPEX’e eklendi) -74.8; duran varlık satışı ✗ +4.7; alınan temettü (FCF_HLD’de) +1.3 'Diğer' içindeki yatırım harcaması (dipnot) CAPEX'e eklendi: +74.8 → |MDV+MODV alımı| içinde</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>VAKKO</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2866.6293248</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2866.6293248</v>
+      </c>
+      <c r="E132" t="n">
+        <v>711.7426176</v>
+      </c>
+      <c r="F132" t="n">
+        <v>711.7426176</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 475.8); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -732.3; duran varlık satışı ✗ +0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>VAKKO</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2577.4913248</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2577.4913248</v>
+      </c>
+      <c r="E133" t="n">
+        <v>856.9036176</v>
+      </c>
+      <c r="F133" t="n">
+        <v>856.9036176</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 466.5); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +474.8; duran varlık satışı ✗ +0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>VANGD</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>-3.82360780000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-3.82360780000001</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.969642600000002</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.969642600000002</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 0.5); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +4.5; duran varlık satışı ✗ +0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>VANGD</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0.3835984</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3835984</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.947968</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.947968</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 0.5); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -8.1; duran varlık satışı ✗ +0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>YAYLA</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>36.973077</v>
+      </c>
+      <c r="D136" t="n">
+        <v>36.973077</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 3.7); kalemler (TTM, mn TL): verilen avans/borç ✗ -116.0; yatırım amaçlı gayrimenkul kira geliri ✗ +7.6; duran varlık satışı ✗ +2.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>YAYLA</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>-10.6146252</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-10.6146252</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 1.1); kalemler (TTM, mn TL): verilen avans/borç ✗ -51.4; duran varlık satışı ✗ +4.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>YAYLA</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>44.5690838</v>
+      </c>
+      <c r="D138" t="n">
+        <v>44.5690838</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>BELGE</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 4.5); kalemler (TTM, mn TL): verilen avans/borç ✗ -108.6; duran varlık satışı ✗ +12.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>YAYLA</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>-17.381376</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-17.381376</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.8349183999999999</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.8349183999999999</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 1.7); kalemler (TTM, mn TL): verilen avans/borç ✗ +19.9; duran varlık satışı ✗ +12.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>YAYLA</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>-6.6600441</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-6.6600441</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.5984263</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.5984263</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 0.6); kalemler (TTM, mn TL): verilen avans/borç ✗ +14.1; duran varlık satışı ✗ +11.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>YAYLA</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>-8.903376</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-8.903376</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.7829184</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.7829184</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>KOŞULLU</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>KESİN</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>EVO (belgeyle teyitli)</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 0.8); kalemler (TTM, mn TL): duran varlık satışı ✗ +14.6; verilen avans/borç ✗ +1.5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="150" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kod</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dönem</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FCF · TTM (mn TL)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Açıklama</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ASUZU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>-1566.2275161</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kontrol 9: belgeden sınıflanamayan artık 1,826.6 &gt; eşik 939.7; 'Diğer' satırının içeriği dipnotlarda açıklanmıyor (tutar ve dipnot referansı arandı). kalemler (TTM, mn TL): SINIFLANMADI +1,826.6; duran varlık satışı ✗ +26.7 · C: 2024/09 raporunun cari sütunu (karşılaştırmalı sütunda Diğer ayrışmadı)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ATATP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>-41.2958189</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 509.1); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ -855.2; duran varlık satışı ✗ +106.5 | KOŞULLU nedeni: Kontrol 11 (sunum değişikliği; TTM penceresinde iki farklı sunum bazı) — V7: Kontrol 11: sunum değişikliği (finansal yatırımlar yatırım → işletme), TTM köprüsü tutarsız esas</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ATATP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>-2525.7763152</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Kontrol 9 artığı belgeden sınıflandı (sınıflanmayan 0.0 ≤ eşik 512.8); kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +1,504.5; duran varlık satışı ✗ +106.7 | KOŞULLU nedeni: Kontrol 11 (sunum değişikliği; TTM penceresinde iki farklı sunum bazı) — V7: Kontrol 11: sunum değişikliği (finansal yatırımlar yatırım → işletme), TTM köprüsü tutarsız esas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ENDAE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-162.0886464</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Kontrol 9: belgeden sınıflanamayan artık 138.8 &gt; eşik 74.5; 'Diğer' satırının içeriği dipnotlarda açıklanmıyor (tutar ve dipnot referansı arandı). kalemler (TTM, mn TL): verilen avans/borç ✗ -192.1; SINIFLANMADI +138.8; menkul kıymet/fon/türev ✗ -31.5; duran varlık satışı ✗ -1.5 · C: 2025/06 raporunun cari sütunu (karşılaştırmalı sütunda Diğer ayrışmadı)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GUBRF</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>9811.105055</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Kontrol 9: belgeden sınıflanamayan artık -1,515.3 &gt; eşik 1,208.4; 'Diğer' satırının içeriği dipnotlarda açıklanmıyor (tutar ve dipnot referansı arandı). kalemler (TTM, mn TL): SINIFLANMADI -1,515.3; duran varlık satışı ✗ +16.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HEKTS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>647.4315264000001</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Kontrol 9: belgeden sınıflanamayan artık 886.6 &gt; eşik 636.1; 'Diğer' satırının içeriği dipnotlarda açıklanmıyor (tutar ve dipnot referansı arandı). kalemler (TTM, mn TL): verilen avans/borç ✗ -1,264.9; SINIFLANMADI +886.6; duran varlık satışı ✗ +11.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HEKTS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-529.0064508</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Kontrol 9: belgeden sınıflanamayan artık 973.7 &gt; eşik 752.0; 'Diğer' satırının içeriği dipnotlarda açıklanmıyor (tutar ve dipnot referansı arandı). kalemler (TTM, mn TL): iştirak/bağlı ortaklık (M&amp;A) ✗ +1,158.3; SINIFLANMADI +973.7; verilen avans/borç ✗ -417.0; duran varlık satışı ✗ +27.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PRKAB</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025/09</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-1540.8742465</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Kontrol 9: belgeden sınıflanamayan artık 233.5 &gt; eşik 139.5; 'Diğer' satırının içeriği dipnotlarda açıklanmıyor (tutar ve dipnot referansı arandı). kalemler (TTM, mn TL): SINIFLANMADI +233.5; alınan faiz ✗ +160.7; menkul kıymet/fon/türev ✗ +131.5; duran varlık satışı ✗ +2.9 · C: 2024/09 raporunun cari sütunu (karşılaştırmalı sütunda Diğer ayrışmadı)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PSDTC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025/03</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4.730214</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Kontrol 9: belgeden sınıflanamayan artık -4.8 &gt; eşik 0.9; 'Diğer' satırının içeriği dipnotlarda açıklanmıyor (tutar ve dipnot referansı arandı). kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +72.5; SINIFLANMADI -4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PSDTC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025/06</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>-2.53628279999999</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Kontrol 9: belgeden sınıflanamayan artık -4.9 &gt; eşik 0.2; 'Diğer' satırının içeriği dipnotlarda açıklanmıyor (tutar ve dipnot referansı arandı). kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +75.2; SINIFLANMADI -4.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QUAGR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025/12</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>592.0419328</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Kontrol 9: belgeden sınıflanamayan artık -225.1 &gt; eşik 109.1; 'Diğer' satırının içeriği dipnotlarda açıklanmıyor (tutar ve dipnot referansı arandı). kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +441.2; alınan faiz ✗ +400.4; SINIFLANMADI -225.1; duran varlık satışı ✗ +27.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QUAGR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1043.3640985</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Kontrol 9: belgeden sınıflanamayan artık -225.1 &gt; eşik 145.3; 'Diğer' satırının içeriği dipnotlarda açıklanmıyor (tutar ve dipnot referansı arandı). kalemler (TTM, mn TL): menkul kıymet/fon/türev ✗ +296.2; SINIFLANMADI -225.1; alınan faiz ✗ +128.0; duran varlık satışı ✗ +23.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QUAGR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>106.1629328</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Kontrol 9: belgeden sınıflanamayan artık -80.3 &gt; eşik 57.3; 'Diğer' satırının içeriği dipnotlarda açıklanmıyor (tutar ve dipnot referansı arandı). kalemler (TTM, mn TL): duran varlık satışı ✗ +230.4; menkul kıymet/fon/türev ✗ +130.4; SINIFLANMADI -80.3; alınan faiz ✗ +59.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ULUSE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1014.4838978</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Kontrol 9: belgeden sınıflanamayan artık -158.4 &gt; eşik 130.1; 'Diğer' satırının içeriği dipnotlarda açıklanmıyor (tutar ve dipnot referansı arandı). kalemler (TTM, mn TL): SINIFLANMADI -158.4; duran varlık satışı ✗ -38.7; verilen avans/borç ✗ -31.5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="100" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kod</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dönem</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Önceki kategori</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Yeni kategori</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Neden</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ANA LİSTE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>KOŞULLU ANA LİSTE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bölüm F: son 3 çeyrek TTM FCF negatif; FCF artık KESİN (önceden KOŞULLU olduğu için ASKIDA idi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ANA LİSTE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>KOŞULLU ANA LİSTE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>aynı</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>